--- a/apps/web/public/examples/example-schedule.xlsx
+++ b/apps/web/public/examples/example-schedule.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="238">
   <si>
     <t>Term</t>
   </si>
@@ -97,7 +97,7 @@
     <t>Chair release</t>
   </si>
   <si>
-    <t>SYNTHETIC: AY, one row per spread term</t>
+    <t>Split over fall and spring</t>
   </si>
   <si>
     <t>SP</t>
@@ -106,411 +106,549 @@
     <t>SP-Full</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Ben Sample</t>
+  </si>
+  <si>
+    <t>Research release</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>Eli Specimen</t>
+  </si>
+  <si>
+    <t>Advising coordinator</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>Ben Sample</t>
-  </si>
-  <si>
-    <t>Sabbatical</t>
-  </si>
-  <si>
-    <t>DATA</t>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:40:00</t>
+  </si>
+  <si>
+    <t>SB 110</t>
+  </si>
+  <si>
+    <t>Data Computing</t>
+  </si>
+  <si>
+    <t>Fay Mockson</t>
+  </si>
+  <si>
+    <t>Lecture</t>
+  </si>
+  <si>
+    <t>In-Person</t>
   </si>
   <si>
     <t>301</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>TR</t>
+    <t>MWF</t>
+  </si>
+  <si>
+    <t>11:00:00 - 12:05:00</t>
+  </si>
+  <si>
+    <t>Machine Learning</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:55:00</t>
+  </si>
+  <si>
+    <t>Data Science Capstone</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>14:10:00 - 15:50:00</t>
   </si>
   <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>FA-First</t>
+  </si>
+  <si>
+    <t>Data Ethics</t>
+  </si>
+  <si>
+    <t>First half of the term</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>Second</t>
+  </si>
+  <si>
+    <t>FA-Second</t>
+  </si>
+  <si>
+    <t>Data Visualization</t>
+  </si>
+  <si>
+    <t>Second half of the term</t>
+  </si>
+  <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>Optimization</t>
+  </si>
+  <si>
+    <t>Also listed as STAT 385</t>
+  </si>
+  <si>
+    <t>STAT 385</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>MATH</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>MTWRF</t>
+  </si>
+  <si>
+    <t>09:00:00 - 11:30:00</t>
+  </si>
+  <si>
+    <t>NH 101</t>
+  </si>
+  <si>
+    <t>WI-Full</t>
+  </si>
+  <si>
+    <t>Mathematics and Music</t>
+  </si>
+  <si>
+    <t>Cy Fictional</t>
+  </si>
+  <si>
+    <t>Winter intensive: meets every weekday for two weeks</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>09:15:00 - 10:20:00</t>
+  </si>
+  <si>
+    <t>Calculus I</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>SU-Second</t>
+  </si>
+  <si>
+    <t>Summer session II</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Calculus I (second semester)</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:20:00</t>
+  </si>
+  <si>
+    <t>NH 102</t>
+  </si>
+  <si>
+    <t>Calculus II</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>10:20:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>NH 103</t>
+  </si>
+  <si>
+    <t>Linear Algebra</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>Multivariable Calculus</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:05:00</t>
+  </si>
+  <si>
+    <t>Discrete Mathematics</t>
+  </si>
+  <si>
+    <t>351</t>
+  </si>
+  <si>
     <t>NH 104</t>
   </si>
   <si>
-    <t>Topics</t>
-  </si>
-  <si>
-    <t>Lecture</t>
-  </si>
-  <si>
-    <t>In-Person</t>
-  </si>
-  <si>
-    <t>STAT 305, MATH 307</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>MWF</t>
-  </si>
-  <si>
-    <t>11:00:00 - 12:05:00</t>
-  </si>
-  <si>
-    <t>NH 103</t>
-  </si>
-  <si>
-    <t>Optimization</t>
-  </si>
-  <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>STAT 385</t>
-  </si>
-  <si>
-    <t>EDUC</t>
-  </si>
-  <si>
-    <t>346</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>1.8</t>
+    <t>Real Analysis I</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>Real Analysis II</t>
+  </si>
+  <si>
+    <t>STAT</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>13:00:00 - 15:30:00</t>
+  </si>
+  <si>
+    <t>NH 105</t>
+  </si>
+  <si>
+    <t>Sports Analytics</t>
+  </si>
+  <si>
+    <t>13:30:00 - 14:35:00</t>
+  </si>
+  <si>
+    <t>Introduction to Statistics</t>
+  </si>
+  <si>
+    <t>Dee Placeholder</t>
+  </si>
+  <si>
+    <t>SU-First</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Summer session I</t>
+  </si>
+  <si>
+    <t>14:45:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>Statistical Methods</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>Regression</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>Eli Specimen, Dee Placeholder</t>
+  </si>
+  <si>
+    <t>SectionId</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>AcademicYear</t>
+  </si>
+  <si>
+    <t>MinimumCredits</t>
+  </si>
+  <si>
+    <t>MaximumCredits</t>
+  </si>
+  <si>
+    <t>StartTime</t>
+  </si>
+  <si>
+    <t>MeetingDuration</t>
+  </si>
+  <si>
+    <t>Classroom</t>
+  </si>
+  <si>
+    <t>CourseLevel</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>EnrollmentDay10</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH143-A</t>
+  </si>
+  <si>
+    <t>AY25</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH143-B</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH162-A</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH231-A</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH256-A</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>AY25-FA-MATH351-A</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>AY25-FA-STAT143-A</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>AY25-FA-STAT143-B</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>AY25-FA-STAT243-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-STAT343-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DATA202-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DATA380-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DATA381-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DATA385-A</t>
+  </si>
+  <si>
+    <t>AY25-WI-MATH110-A</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>AY25-WI-STAT130-A</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>AY25-SP-MATH144-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-MATH162-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-MATH232-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-MATH352-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-STAT143-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-STAT244-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DATA301-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DATA302-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-MATH143-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-STAT143-A</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Load</t>
+  </si>
+  <si>
+    <t>AY</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Choose</t>
+  </si>
+  <si>
+    <t>Bound</t>
+  </si>
+  <si>
+    <t>Gap</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Starts</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>DayRule</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>Meets</t>
+  </si>
+  <si>
+    <t>Intensive terms meet daily</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>WI, SU</t>
+  </si>
+  <si>
+    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
+  </si>
+  <si>
+    <t>allow</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>StartWeek</t>
+  </si>
+  <si>
+    <t>EndWeek</t>
+  </si>
+  <si>
+    <t>SpreadTerm</t>
+  </si>
+  <si>
+    <t>NonRoom</t>
   </si>
   <si>
     <t>Off Campus</t>
   </si>
   <si>
-    <t>Internship</t>
-  </si>
-  <si>
-    <t>Kim</t>
-  </si>
-  <si>
-    <t>Might be 1.8 hours</t>
-  </si>
-  <si>
-    <t>MATH</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>09:15:00 - 10:20:00</t>
-  </si>
-  <si>
-    <t>NH 101</t>
-  </si>
-  <si>
-    <t>Calculus</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MW
-F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:15:00 - 10:20:00
-10:20:00 - 11:10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH 101
-NH 102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65
-50</t>
-  </si>
-  <si>
-    <t>Linear Algebra</t>
-  </si>
-  <si>
-    <t>Ada Example, Ben Sample</t>
-  </si>
-  <si>
-    <t>SU</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MWF
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08:00:00 - 09:05:00
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH 105
-Online</t>
-  </si>
-  <si>
-    <t>SU-Full</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65
-</t>
-  </si>
-  <si>
-    <t>Summer Topics</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>MTWRF</t>
-  </si>
-  <si>
-    <t>13:00:00 - 13:50:00</t>
-  </si>
-  <si>
-    <t>NH 106</t>
-  </si>
-  <si>
-    <t>First</t>
-  </si>
-  <si>
-    <t>SU-First</t>
-  </si>
-  <si>
-    <t>Half Term</t>
-  </si>
-  <si>
-    <t>STAT</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TR
-TR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:20:00 - 12:00:00
-10:20:00 - 12:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NH 1
-NH 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100
-100</t>
-  </si>
-  <si>
-    <t>Statistics</t>
-  </si>
-  <si>
-    <t>Online</t>
-  </si>
-  <si>
-    <t>SectionId</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>AcademicYear</t>
-  </si>
-  <si>
-    <t>MinimumCredits</t>
-  </si>
-  <si>
-    <t>MaximumCredits</t>
-  </si>
-  <si>
-    <t>StartTime</t>
-  </si>
-  <si>
-    <t>MeetingDuration</t>
-  </si>
-  <si>
-    <t>Classroom</t>
-  </si>
-  <si>
-    <t>CourseLevel</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Enrollment</t>
-  </si>
-  <si>
-    <t>EnrollmentDay10</t>
-  </si>
-  <si>
-    <t>R1-FA-MATH101-A</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>R1-SP-MATH102-A</t>
-  </si>
-  <si>
-    <t>Ada Example (3), Ben Sample (1)</t>
-  </si>
-  <si>
-    <t>MW</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>NH 102</t>
-  </si>
-  <si>
-    <t>R1-FA-STAT201-A</t>
-  </si>
-  <si>
-    <t>NH 1</t>
-  </si>
-  <si>
-    <t>NH 2</t>
-  </si>
-  <si>
-    <t>R1-FA-EDUC346-J</t>
-  </si>
-  <si>
-    <t>R1-FA-DATA385-A</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>R1-SP-DATA301-A</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>R1-SU-MATH150-A</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>NH 105</t>
-  </si>
-  <si>
-    <t>R1-SU-MATH160-A</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>307</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Load</t>
-  </si>
-  <si>
-    <t>AY</t>
-  </si>
-  <si>
-    <t>Constraint</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Course</t>
-  </si>
-  <si>
-    <t>Instructor</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Choose</t>
-  </si>
-  <si>
-    <t>Bound</t>
-  </si>
-  <si>
-    <t>Gap</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Starts</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>DayRule</t>
-  </si>
-  <si>
-    <t>From</t>
-  </si>
-  <si>
-    <t>To</t>
-  </si>
-  <si>
-    <t>Should</t>
-  </si>
-  <si>
-    <t>Meets</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>StartWeek</t>
-  </si>
-  <si>
-    <t>EndWeek</t>
-  </si>
-  <si>
-    <t>SpreadTerm</t>
-  </si>
-  <si>
-    <t>NonRoom</t>
-  </si>
-  <si>
     <t>TBD</t>
   </si>
   <si>
     <t>Fall</t>
   </si>
   <si>
-    <t>WI</t>
-  </si>
-  <si>
     <t>Winter Intensive</t>
   </si>
   <si>
@@ -529,18 +667,12 @@
     <t>First half</t>
   </si>
   <si>
-    <t>Second</t>
-  </si>
-  <si>
     <t>Second half</t>
   </si>
   <si>
     <t>Intensive A</t>
   </si>
   <si>
-    <t>B</t>
-  </si>
-  <si>
     <t>Intensive B</t>
   </si>
   <si>
@@ -574,7 +706,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>10:15:43</t>
+    <t>10:29:00</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -637,12 +769,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -982,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -995,12 +1124,12 @@
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="25" customWidth="1"/>
-    <col min="15" max="15" width="21" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="14" max="14" width="31" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="40" customWidth="1"/>
-    <col min="18" max="18" width="20" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1229,114 +1358,114 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
         <v>32</v>
       </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5">
-        <v>100</v>
+        <v>23</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P5" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="Q5" t="s">
         <v>19</v>
       </c>
       <c r="R5" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" t="s">
-        <v>29</v>
-      </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
         <v>22</v>
       </c>
       <c r="K6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6">
-        <v>65</v>
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="P6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="Q6" t="s">
         <v>19</v>
       </c>
       <c r="R6" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1344,28 +1473,28 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="J7" t="s">
         <v>22</v>
@@ -1373,23 +1502,23 @@
       <c r="K7" t="s">
         <v>23</v>
       </c>
-      <c r="L7" t="s">
-        <v>19</v>
+      <c r="L7">
+        <v>100</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="N7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="O7" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="P7" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="Q7" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="R7" t="s">
         <v>19</v>
@@ -1397,52 +1526,52 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="I8" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
       </c>
       <c r="K8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L8">
         <v>65</v>
       </c>
       <c r="M8" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="N8" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="O8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q8" t="s">
         <v>19</v>
@@ -1456,28 +1585,28 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>67</v>
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" t="s">
+        <v>41</v>
       </c>
       <c r="J9" t="s">
         <v>22</v>
@@ -1485,20 +1614,20 @@
       <c r="K9" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>68</v>
+      <c r="L9">
+        <v>100</v>
       </c>
       <c r="M9" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="N9" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="O9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="s">
         <v>19</v>
@@ -1509,55 +1638,55 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10">
+        <v>100</v>
+      </c>
+      <c r="M10" t="s">
         <v>58</v>
       </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J10" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="M10" t="s">
-        <v>79</v>
-      </c>
       <c r="N10" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="O10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P10" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="R10" t="s">
         <v>19</v>
@@ -1565,55 +1694,55 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="J11" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="K11" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="L11">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M11" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="N11" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="O11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P11" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="Q11" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="R11" t="s">
         <v>19</v>
@@ -1624,28 +1753,28 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>91</v>
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" t="s">
+        <v>41</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
@@ -1653,25 +1782,1145 @@
       <c r="K12" t="s">
         <v>23</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="L12">
+        <v>65</v>
+      </c>
+      <c r="M12" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" t="s">
+        <v>44</v>
+      </c>
+      <c r="P12" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>67</v>
+      </c>
+      <c r="R12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s">
+        <v>74</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" t="s">
+        <v>75</v>
+      </c>
+      <c r="L13">
+        <v>150</v>
+      </c>
+      <c r="M13" t="s">
+        <v>76</v>
+      </c>
+      <c r="N13" t="s">
+        <v>77</v>
+      </c>
+      <c r="O13" t="s">
+        <v>44</v>
+      </c>
+      <c r="P13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>78</v>
+      </c>
+      <c r="R13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" t="s">
+        <v>74</v>
+      </c>
+      <c r="J14" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14">
+        <v>65</v>
+      </c>
+      <c r="M14" t="s">
+        <v>81</v>
+      </c>
+      <c r="N14" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>19</v>
+      </c>
+      <c r="R14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" t="s">
+        <v>72</v>
+      </c>
+      <c r="H15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L15">
+        <v>150</v>
+      </c>
+      <c r="M15" t="s">
+        <v>81</v>
+      </c>
+      <c r="N15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" t="s">
+        <v>44</v>
+      </c>
+      <c r="P15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>84</v>
+      </c>
+      <c r="R15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16">
+        <v>65</v>
+      </c>
+      <c r="M16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N16" t="s">
+        <v>24</v>
+      </c>
+      <c r="O16" t="s">
+        <v>44</v>
+      </c>
+      <c r="P16" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>19</v>
+      </c>
+      <c r="R16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17">
+        <v>65</v>
+      </c>
+      <c r="M17" t="s">
+        <v>87</v>
+      </c>
+      <c r="N17" t="s">
+        <v>24</v>
+      </c>
+      <c r="O17" t="s">
+        <v>44</v>
+      </c>
+      <c r="P17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>19</v>
+      </c>
+      <c r="R17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" t="s">
+        <v>90</v>
+      </c>
+      <c r="J18" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18">
+        <v>65</v>
+      </c>
+      <c r="M18" t="s">
+        <v>91</v>
+      </c>
+      <c r="N18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>19</v>
+      </c>
+      <c r="R18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" t="s">
+        <v>90</v>
+      </c>
+      <c r="J19" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19">
+        <v>65</v>
+      </c>
+      <c r="M19" t="s">
+        <v>91</v>
+      </c>
+      <c r="N19" t="s">
+        <v>30</v>
+      </c>
+      <c r="O19" t="s">
+        <v>44</v>
+      </c>
+      <c r="P19" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>19</v>
+      </c>
+      <c r="R19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" t="s">
         <v>92</v>
       </c>
-      <c r="M12" t="s">
+      <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" t="s">
         <v>93</v>
       </c>
-      <c r="N12" t="s">
+      <c r="I20" t="s">
+        <v>94</v>
+      </c>
+      <c r="J20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20">
+        <v>100</v>
+      </c>
+      <c r="M20" t="s">
+        <v>95</v>
+      </c>
+      <c r="N20" t="s">
+        <v>77</v>
+      </c>
+      <c r="O20" t="s">
+        <v>44</v>
+      </c>
+      <c r="P20" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>19</v>
+      </c>
+      <c r="R20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21">
+        <v>100</v>
+      </c>
+      <c r="M21" t="s">
+        <v>97</v>
+      </c>
+      <c r="N21" t="s">
+        <v>77</v>
+      </c>
+      <c r="O21" t="s">
+        <v>44</v>
+      </c>
+      <c r="P21" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>19</v>
+      </c>
+      <c r="R21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" t="s">
         <v>47</v>
       </c>
-      <c r="O12" t="s">
+      <c r="H22" t="s">
+        <v>99</v>
+      </c>
+      <c r="I22" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22">
+        <v>65</v>
+      </c>
+      <c r="M22" t="s">
+        <v>100</v>
+      </c>
+      <c r="N22" t="s">
+        <v>77</v>
+      </c>
+      <c r="O22" t="s">
+        <v>44</v>
+      </c>
+      <c r="P22" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>19</v>
+      </c>
+      <c r="R22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" t="s">
         <v>39</v>
       </c>
-      <c r="P12" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>19</v>
-      </c>
-      <c r="R12" t="s">
+      <c r="H23" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" t="s">
+        <v>102</v>
+      </c>
+      <c r="J23" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23">
+        <v>100</v>
+      </c>
+      <c r="M23" t="s">
+        <v>103</v>
+      </c>
+      <c r="N23" t="s">
+        <v>30</v>
+      </c>
+      <c r="O23" t="s">
+        <v>44</v>
+      </c>
+      <c r="P23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>19</v>
+      </c>
+      <c r="R23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" t="s">
+        <v>102</v>
+      </c>
+      <c r="J24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24">
+        <v>100</v>
+      </c>
+      <c r="M24" t="s">
+        <v>105</v>
+      </c>
+      <c r="N24" t="s">
+        <v>30</v>
+      </c>
+      <c r="O24" t="s">
+        <v>44</v>
+      </c>
+      <c r="P24" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>19</v>
+      </c>
+      <c r="R24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" t="s">
+        <v>108</v>
+      </c>
+      <c r="I25" t="s">
+        <v>109</v>
+      </c>
+      <c r="J25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" t="s">
+        <v>75</v>
+      </c>
+      <c r="L25">
+        <v>150</v>
+      </c>
+      <c r="M25" t="s">
+        <v>110</v>
+      </c>
+      <c r="N25" t="s">
+        <v>33</v>
+      </c>
+      <c r="O25" t="s">
+        <v>44</v>
+      </c>
+      <c r="P25" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>19</v>
+      </c>
+      <c r="R25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" t="s">
+        <v>38</v>
+      </c>
+      <c r="G26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" t="s">
+        <v>111</v>
+      </c>
+      <c r="I26" t="s">
+        <v>109</v>
+      </c>
+      <c r="J26" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26">
+        <v>65</v>
+      </c>
+      <c r="M26" t="s">
+        <v>112</v>
+      </c>
+      <c r="N26" t="s">
+        <v>113</v>
+      </c>
+      <c r="O26" t="s">
+        <v>44</v>
+      </c>
+      <c r="P26" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>19</v>
+      </c>
+      <c r="R26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" t="s">
+        <v>111</v>
+      </c>
+      <c r="I27" t="s">
+        <v>109</v>
+      </c>
+      <c r="J27" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27">
+        <v>65</v>
+      </c>
+      <c r="M27" t="s">
+        <v>112</v>
+      </c>
+      <c r="N27" t="s">
+        <v>113</v>
+      </c>
+      <c r="O27" t="s">
+        <v>44</v>
+      </c>
+      <c r="P27" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>19</v>
+      </c>
+      <c r="R27" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s">
+        <v>109</v>
+      </c>
+      <c r="J28" t="s">
+        <v>56</v>
+      </c>
+      <c r="K28" t="s">
+        <v>114</v>
+      </c>
+      <c r="L28">
+        <v>150</v>
+      </c>
+      <c r="M28" t="s">
+        <v>112</v>
+      </c>
+      <c r="N28" t="s">
+        <v>113</v>
+      </c>
+      <c r="O28" t="s">
+        <v>44</v>
+      </c>
+      <c r="P28" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>116</v>
+      </c>
+      <c r="R28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G29" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" t="s">
+        <v>117</v>
+      </c>
+      <c r="I29" t="s">
+        <v>109</v>
+      </c>
+      <c r="J29" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29">
+        <v>65</v>
+      </c>
+      <c r="M29" t="s">
+        <v>112</v>
+      </c>
+      <c r="N29" t="s">
+        <v>113</v>
+      </c>
+      <c r="O29" t="s">
+        <v>44</v>
+      </c>
+      <c r="P29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>19</v>
+      </c>
+      <c r="R29" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30" t="s">
+        <v>93</v>
+      </c>
+      <c r="I30" t="s">
+        <v>109</v>
+      </c>
+      <c r="J30" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30">
+        <v>100</v>
+      </c>
+      <c r="M30" t="s">
+        <v>119</v>
+      </c>
+      <c r="N30" t="s">
+        <v>33</v>
+      </c>
+      <c r="O30" t="s">
+        <v>44</v>
+      </c>
+      <c r="P30" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>19</v>
+      </c>
+      <c r="R30" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H31" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" t="s">
+        <v>109</v>
+      </c>
+      <c r="J31" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31">
+        <v>100</v>
+      </c>
+      <c r="M31" t="s">
+        <v>121</v>
+      </c>
+      <c r="N31" t="s">
+        <v>33</v>
+      </c>
+      <c r="O31" t="s">
+        <v>44</v>
+      </c>
+      <c r="P31" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>19</v>
+      </c>
+      <c r="R31" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" t="s">
+        <v>38</v>
+      </c>
+      <c r="F32" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32" t="s">
+        <v>39</v>
+      </c>
+      <c r="H32" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32" t="s">
+        <v>109</v>
+      </c>
+      <c r="J32" t="s">
+        <v>22</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32">
+        <v>100</v>
+      </c>
+      <c r="M32" t="s">
+        <v>123</v>
+      </c>
+      <c r="N32" t="s">
+        <v>124</v>
+      </c>
+      <c r="O32" t="s">
+        <v>44</v>
+      </c>
+      <c r="P32" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>19</v>
+      </c>
+      <c r="R32" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1683,42 +2932,42 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="9" max="9" width="33" customWidth="1"/>
+    <col min="9" max="9" width="31" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="30" customWidth="1"/>
     <col min="18" max="18" width="21" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="7" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="22" width="20" customWidth="1"/>
+    <col min="22" max="22" width="40" customWidth="1"/>
     <col min="23" max="23" width="12" customWidth="1"/>
     <col min="24" max="24" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -1742,22 +2991,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -1766,10 +3015,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -1778,21 +3027,21 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
         <v>18</v>
@@ -1801,16 +3050,16 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -1822,22 +3071,22 @@
         <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N2" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="O2">
         <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="Q2" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="R2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S2" t="s">
         <v>19</v>
@@ -1846,7 +3095,7 @@
         <v>19</v>
       </c>
       <c r="U2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V2" t="s">
         <v>19</v>
@@ -1860,31 +3109,31 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1896,22 +3145,22 @@
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="N3" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="O3">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="Q3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="R3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S3" t="s">
         <v>19</v>
@@ -1920,7 +3169,7 @@
         <v>19</v>
       </c>
       <c r="U3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V3" t="s">
         <v>19</v>
@@ -1934,31 +3183,31 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>111</v>
+        <v>30</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1970,22 +3219,22 @@
         <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="N4" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="O4">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="P4" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="Q4" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="R4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S4" t="s">
         <v>19</v>
@@ -1994,7 +3243,7 @@
         <v>19</v>
       </c>
       <c r="U4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V4" t="s">
         <v>19</v>
@@ -2008,13 +3257,13 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
@@ -2023,16 +3272,16 @@
         <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="G5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -2044,22 +3293,22 @@
         <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N5" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="Q5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="R5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S5" t="s">
         <v>19</v>
@@ -2068,7 +3317,7 @@
         <v>19</v>
       </c>
       <c r="U5" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="V5" t="s">
         <v>19</v>
@@ -2082,13 +3331,13 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -2097,16 +3346,16 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="G6" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -2118,22 +3367,22 @@
         <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="N6" t="s">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="O6">
+        <v>65</v>
+      </c>
+      <c r="P6" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q6" t="s">
         <v>100</v>
       </c>
-      <c r="P6" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>93</v>
-      </c>
       <c r="R6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S6" t="s">
         <v>19</v>
@@ -2142,7 +3391,7 @@
         <v>19</v>
       </c>
       <c r="U6" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="V6" t="s">
         <v>19</v>
@@ -2156,13 +3405,13 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -2171,43 +3420,43 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="J7">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L7" t="s">
         <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="N7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7" t="s">
-        <v>19</v>
+        <v>149</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="Q7" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="R7" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="S7" t="s">
         <v>19</v>
@@ -2216,10 +3465,10 @@
         <v>19</v>
       </c>
       <c r="U7" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="V7" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="W7" t="s">
         <v>19</v>
@@ -2230,13 +3479,13 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -2245,16 +3494,16 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2266,31 +3515,31 @@
         <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="N8" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="O8">
         <v>65</v>
       </c>
       <c r="P8" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>112</v>
+      </c>
+      <c r="R8" t="s">
+        <v>44</v>
+      </c>
+      <c r="S8" t="s">
+        <v>19</v>
+      </c>
+      <c r="T8" t="s">
+        <v>19</v>
+      </c>
+      <c r="U8" t="s">
         <v>45</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>46</v>
-      </c>
-      <c r="R8" t="s">
-        <v>39</v>
-      </c>
-      <c r="S8" t="s">
-        <v>19</v>
-      </c>
-      <c r="T8" t="s">
-        <v>19</v>
-      </c>
-      <c r="U8" t="s">
-        <v>40</v>
       </c>
       <c r="V8" t="s">
         <v>19</v>
@@ -2304,31 +3553,31 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -2340,22 +3589,22 @@
         <v>19</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="N9" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="Q9" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="R9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S9" t="s">
         <v>19</v>
@@ -2364,7 +3613,7 @@
         <v>19</v>
       </c>
       <c r="U9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V9" t="s">
         <v>19</v>
@@ -2378,58 +3627,58 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10" t="s">
         <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N10" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="O10">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="Q10" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="R10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S10" t="s">
         <v>19</v>
@@ -2438,7 +3687,7 @@
         <v>19</v>
       </c>
       <c r="U10" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V10" t="s">
         <v>19</v>
@@ -2452,58 +3701,58 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I11" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" t="s">
         <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="N11" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11" t="s">
-        <v>19</v>
+        <v>143</v>
+      </c>
+      <c r="O11">
+        <v>100</v>
       </c>
       <c r="P11" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="Q11" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="R11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S11" t="s">
         <v>19</v>
@@ -2512,7 +3761,7 @@
         <v>19</v>
       </c>
       <c r="U11" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="V11" t="s">
         <v>19</v>
@@ -2526,75 +3775,1185 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12">
+        <v>4</v>
+      </c>
+      <c r="K12">
+        <v>4</v>
+      </c>
+      <c r="L12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" t="s">
+        <v>147</v>
+      </c>
+      <c r="O12">
+        <v>100</v>
+      </c>
+      <c r="P12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>42</v>
+      </c>
+      <c r="R12" t="s">
+        <v>44</v>
+      </c>
+      <c r="S12" t="s">
+        <v>19</v>
+      </c>
+      <c r="T12" t="s">
+        <v>19</v>
+      </c>
+      <c r="U12" t="s">
+        <v>45</v>
+      </c>
+      <c r="V12" t="s">
+        <v>19</v>
+      </c>
+      <c r="W12" t="s">
+        <v>19</v>
+      </c>
+      <c r="X12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" t="s">
+        <v>39</v>
+      </c>
+      <c r="N13" t="s">
+        <v>149</v>
+      </c>
+      <c r="O13">
+        <v>100</v>
+      </c>
+      <c r="P13" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>58</v>
+      </c>
+      <c r="R13" t="s">
+        <v>44</v>
+      </c>
+      <c r="S13" t="s">
+        <v>19</v>
+      </c>
+      <c r="T13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U13" t="s">
+        <v>45</v>
+      </c>
+      <c r="V13" t="s">
+        <v>59</v>
+      </c>
+      <c r="W13" t="s">
+        <v>19</v>
+      </c>
+      <c r="X13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N14" t="s">
+        <v>149</v>
+      </c>
+      <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>63</v>
+      </c>
+      <c r="R14" t="s">
+        <v>44</v>
+      </c>
+      <c r="S14" t="s">
+        <v>19</v>
+      </c>
+      <c r="T14" t="s">
+        <v>19</v>
+      </c>
+      <c r="U14" t="s">
+        <v>45</v>
+      </c>
+      <c r="V14" t="s">
+        <v>64</v>
+      </c>
+      <c r="W14" t="s">
+        <v>19</v>
+      </c>
+      <c r="X14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="K15">
+        <v>4</v>
+      </c>
+      <c r="L15" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" t="s">
+        <v>47</v>
+      </c>
+      <c r="N15" t="s">
+        <v>141</v>
+      </c>
+      <c r="O15">
+        <v>65</v>
+      </c>
+      <c r="P15" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>66</v>
+      </c>
+      <c r="R15" t="s">
+        <v>44</v>
+      </c>
+      <c r="S15" t="s">
+        <v>19</v>
+      </c>
+      <c r="T15" t="s">
+        <v>19</v>
+      </c>
+      <c r="U15" t="s">
+        <v>45</v>
+      </c>
+      <c r="V15" t="s">
+        <v>67</v>
+      </c>
+      <c r="W15" t="s">
+        <v>19</v>
+      </c>
+      <c r="X15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" t="s">
         <v>71</v>
       </c>
-      <c r="E12" t="s">
+      <c r="H16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>4</v>
+      </c>
+      <c r="L16" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" t="s">
+        <v>72</v>
+      </c>
+      <c r="N16" t="s">
+        <v>161</v>
+      </c>
+      <c r="O16">
+        <v>150</v>
+      </c>
+      <c r="P16" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>76</v>
+      </c>
+      <c r="R16" t="s">
+        <v>44</v>
+      </c>
+      <c r="S16" t="s">
+        <v>19</v>
+      </c>
+      <c r="T16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U16" t="s">
+        <v>45</v>
+      </c>
+      <c r="V16" t="s">
+        <v>78</v>
+      </c>
+      <c r="W16" t="s">
+        <v>19</v>
+      </c>
+      <c r="X16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <v>4</v>
+      </c>
+      <c r="L17" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" t="s">
+        <v>72</v>
+      </c>
+      <c r="N17" t="s">
+        <v>163</v>
+      </c>
+      <c r="O17">
+        <v>150</v>
+      </c>
+      <c r="P17" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>110</v>
+      </c>
+      <c r="R17" t="s">
+        <v>44</v>
+      </c>
+      <c r="S17" t="s">
+        <v>19</v>
+      </c>
+      <c r="T17" t="s">
+        <v>19</v>
+      </c>
+      <c r="U17" t="s">
+        <v>45</v>
+      </c>
+      <c r="V17" t="s">
+        <v>19</v>
+      </c>
+      <c r="W17" t="s">
+        <v>19</v>
+      </c>
+      <c r="X17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18">
+        <v>4</v>
+      </c>
+      <c r="K18">
+        <v>4</v>
+      </c>
+      <c r="L18" t="s">
+        <v>19</v>
+      </c>
+      <c r="M18" t="s">
+        <v>47</v>
+      </c>
+      <c r="N18" t="s">
+        <v>139</v>
+      </c>
+      <c r="O18">
+        <v>65</v>
+      </c>
+      <c r="P18" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>87</v>
+      </c>
+      <c r="R18" t="s">
+        <v>44</v>
+      </c>
+      <c r="S18" t="s">
+        <v>19</v>
+      </c>
+      <c r="T18" t="s">
+        <v>19</v>
+      </c>
+      <c r="U18" t="s">
+        <v>45</v>
+      </c>
+      <c r="V18" t="s">
+        <v>19</v>
+      </c>
+      <c r="W18" t="s">
+        <v>19</v>
+      </c>
+      <c r="X18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+      <c r="K19">
+        <v>4</v>
+      </c>
+      <c r="L19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N19" t="s">
+        <v>139</v>
+      </c>
+      <c r="O19">
+        <v>65</v>
+      </c>
+      <c r="P19" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>91</v>
+      </c>
+      <c r="R19" t="s">
+        <v>44</v>
+      </c>
+      <c r="S19" t="s">
+        <v>19</v>
+      </c>
+      <c r="T19" t="s">
+        <v>19</v>
+      </c>
+      <c r="U19" t="s">
+        <v>45</v>
+      </c>
+      <c r="V19" t="s">
+        <v>19</v>
+      </c>
+      <c r="W19" t="s">
+        <v>19</v>
+      </c>
+      <c r="X19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" t="s">
+        <v>96</v>
+      </c>
+      <c r="H20" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" t="s">
+        <v>77</v>
+      </c>
+      <c r="J20">
+        <v>4</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" t="s">
+        <v>39</v>
+      </c>
+      <c r="N20" t="s">
+        <v>145</v>
+      </c>
+      <c r="O20">
+        <v>100</v>
+      </c>
+      <c r="P20" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>97</v>
+      </c>
+      <c r="R20" t="s">
+        <v>44</v>
+      </c>
+      <c r="S20" t="s">
+        <v>19</v>
+      </c>
+      <c r="T20" t="s">
+        <v>19</v>
+      </c>
+      <c r="U20" t="s">
+        <v>45</v>
+      </c>
+      <c r="V20" t="s">
+        <v>19</v>
+      </c>
+      <c r="W20" t="s">
+        <v>19</v>
+      </c>
+      <c r="X20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I21" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
+      <c r="K21">
+        <v>4</v>
+      </c>
+      <c r="L21" t="s">
+        <v>19</v>
+      </c>
+      <c r="M21" t="s">
+        <v>39</v>
+      </c>
+      <c r="N21" t="s">
+        <v>149</v>
+      </c>
+      <c r="O21">
+        <v>100</v>
+      </c>
+      <c r="P21" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>105</v>
+      </c>
+      <c r="R21" t="s">
+        <v>44</v>
+      </c>
+      <c r="S21" t="s">
+        <v>19</v>
+      </c>
+      <c r="T21" t="s">
+        <v>19</v>
+      </c>
+      <c r="U21" t="s">
+        <v>45</v>
+      </c>
+      <c r="V21" t="s">
+        <v>19</v>
+      </c>
+      <c r="W21" t="s">
+        <v>19</v>
+      </c>
+      <c r="X21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>168</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" t="s">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" t="s">
+        <v>113</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" t="s">
+        <v>47</v>
+      </c>
+      <c r="N22" t="s">
+        <v>151</v>
+      </c>
+      <c r="O22">
+        <v>65</v>
+      </c>
+      <c r="P22" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>112</v>
+      </c>
+      <c r="R22" t="s">
+        <v>44</v>
+      </c>
+      <c r="S22" t="s">
+        <v>19</v>
+      </c>
+      <c r="T22" t="s">
+        <v>19</v>
+      </c>
+      <c r="U22" t="s">
+        <v>45</v>
+      </c>
+      <c r="V22" t="s">
+        <v>19</v>
+      </c>
+      <c r="W22" t="s">
+        <v>19</v>
+      </c>
+      <c r="X22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" t="s">
+        <v>120</v>
+      </c>
+      <c r="H23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="K23">
+        <v>4</v>
+      </c>
+      <c r="L23" t="s">
+        <v>19</v>
+      </c>
+      <c r="M23" t="s">
+        <v>39</v>
+      </c>
+      <c r="N23" t="s">
+        <v>145</v>
+      </c>
+      <c r="O23">
+        <v>100</v>
+      </c>
+      <c r="P23" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>121</v>
+      </c>
+      <c r="R23" t="s">
+        <v>44</v>
+      </c>
+      <c r="S23" t="s">
+        <v>19</v>
+      </c>
+      <c r="T23" t="s">
+        <v>19</v>
+      </c>
+      <c r="U23" t="s">
+        <v>45</v>
+      </c>
+      <c r="V23" t="s">
+        <v>19</v>
+      </c>
+      <c r="W23" t="s">
+        <v>19</v>
+      </c>
+      <c r="X23" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" t="s">
+        <v>43</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="K24">
+        <v>4</v>
+      </c>
+      <c r="L24" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" t="s">
+        <v>47</v>
+      </c>
+      <c r="N24" t="s">
+        <v>141</v>
+      </c>
+      <c r="O24">
+        <v>65</v>
+      </c>
+      <c r="P24" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>49</v>
+      </c>
+      <c r="R24" t="s">
+        <v>44</v>
+      </c>
+      <c r="S24" t="s">
+        <v>19</v>
+      </c>
+      <c r="T24" t="s">
+        <v>19</v>
+      </c>
+      <c r="U24" t="s">
+        <v>45</v>
+      </c>
+      <c r="V24" t="s">
+        <v>19</v>
+      </c>
+      <c r="W24" t="s">
+        <v>19</v>
+      </c>
+      <c r="X24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25">
+        <v>4</v>
+      </c>
+      <c r="K25">
+        <v>4</v>
+      </c>
+      <c r="L25" t="s">
+        <v>19</v>
+      </c>
+      <c r="M25" t="s">
+        <v>39</v>
+      </c>
+      <c r="N25" t="s">
+        <v>143</v>
+      </c>
+      <c r="O25">
+        <v>100</v>
+      </c>
+      <c r="P25" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>52</v>
+      </c>
+      <c r="R25" t="s">
+        <v>44</v>
+      </c>
+      <c r="S25" t="s">
+        <v>19</v>
+      </c>
+      <c r="T25" t="s">
+        <v>19</v>
+      </c>
+      <c r="U25" t="s">
+        <v>45</v>
+      </c>
+      <c r="V25" t="s">
+        <v>19</v>
+      </c>
+      <c r="W25" t="s">
+        <v>19</v>
+      </c>
+      <c r="X25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26" t="s">
+        <v>30</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" t="s">
+        <v>72</v>
+      </c>
+      <c r="N26" t="s">
+        <v>161</v>
+      </c>
+      <c r="O26">
+        <v>150</v>
+      </c>
+      <c r="P26" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>81</v>
+      </c>
+      <c r="R26" t="s">
+        <v>44</v>
+      </c>
+      <c r="S26" t="s">
+        <v>19</v>
+      </c>
+      <c r="T26" t="s">
+        <v>19</v>
+      </c>
+      <c r="U26" t="s">
+        <v>45</v>
+      </c>
+      <c r="V26" t="s">
         <v>84</v>
       </c>
-      <c r="F12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12">
+      <c r="W26" t="s">
+        <v>19</v>
+      </c>
+      <c r="X26" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>173</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I27" t="s">
+        <v>113</v>
+      </c>
+      <c r="J27">
         <v>2</v>
       </c>
-      <c r="K12">
+      <c r="K27">
         <v>2</v>
       </c>
-      <c r="L12" t="s">
-        <v>19</v>
-      </c>
-      <c r="M12" t="s">
-        <v>81</v>
-      </c>
-      <c r="N12" t="s">
-        <v>128</v>
-      </c>
-      <c r="O12">
-        <v>50</v>
-      </c>
-      <c r="P12" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>86</v>
-      </c>
-      <c r="R12" t="s">
-        <v>39</v>
-      </c>
-      <c r="S12" t="s">
-        <v>19</v>
-      </c>
-      <c r="T12" t="s">
-        <v>19</v>
-      </c>
-      <c r="U12" t="s">
-        <v>19</v>
-      </c>
-      <c r="V12" t="s">
-        <v>19</v>
-      </c>
-      <c r="W12" t="s">
-        <v>19</v>
-      </c>
-      <c r="X12" t="s">
+      <c r="L27" t="s">
+        <v>19</v>
+      </c>
+      <c r="M27" t="s">
+        <v>72</v>
+      </c>
+      <c r="N27" t="s">
+        <v>161</v>
+      </c>
+      <c r="O27">
+        <v>150</v>
+      </c>
+      <c r="P27" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>112</v>
+      </c>
+      <c r="R27" t="s">
+        <v>44</v>
+      </c>
+      <c r="S27" t="s">
+        <v>19</v>
+      </c>
+      <c r="T27" t="s">
+        <v>19</v>
+      </c>
+      <c r="U27" t="s">
+        <v>115</v>
+      </c>
+      <c r="V27" t="s">
+        <v>116</v>
+      </c>
+      <c r="W27" t="s">
+        <v>19</v>
+      </c>
+      <c r="X27" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2606,17 +4965,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2627,35 +4986,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2666,31 +5003,30 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -2698,7 +5034,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -2707,7 +5043,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2718,7 +5054,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
         <v>30</v>
@@ -2730,9 +5066,29 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2744,11 +5100,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
@@ -2757,74 +5113,261 @@
     <col min="9" max="9" width="5" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="8" customWidth="1"/>
-    <col min="13" max="14" width="6" customWidth="1"/>
+    <col min="12" max="13" width="8" customWidth="1"/>
+    <col min="14" max="14" width="7" customWidth="1"/>
     <col min="16" max="16" width="6" customWidth="1"/>
     <col min="17" max="17" width="4" customWidth="1"/>
     <col min="18" max="18" width="8" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="20" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>147</v>
+        <v>190</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>196</v>
+      </c>
+      <c r="N2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S2" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>198</v>
+      </c>
+      <c r="K3" t="s">
+        <v>199</v>
+      </c>
+      <c r="L3" t="s">
+        <v>161</v>
+      </c>
+      <c r="M3" t="s">
+        <v>196</v>
+      </c>
+      <c r="N3" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" t="s">
+        <v>19</v>
+      </c>
+      <c r="S3" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>198</v>
+      </c>
+      <c r="K4" t="s">
+        <v>199</v>
+      </c>
+      <c r="L4" t="s">
+        <v>163</v>
+      </c>
+      <c r="M4" t="s">
+        <v>196</v>
+      </c>
+      <c r="N4" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R4" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" t="s">
+        <v>19</v>
+      </c>
+      <c r="T4" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2846,27 +5389,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>153</v>
+        <v>203</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>154</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
@@ -2886,7 +5429,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
@@ -2906,10 +5449,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>207</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -2926,10 +5469,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -2946,10 +5489,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -2972,7 +5515,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
@@ -2989,10 +5532,10 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="D8" t="s">
         <v>19</v>
@@ -3012,7 +5555,7 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>161</v>
+        <v>211</v>
       </c>
       <c r="D9" t="s">
         <v>19</v>
@@ -3029,10 +5572,10 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>162</v>
+        <v>212</v>
       </c>
       <c r="D10" t="s">
         <v>19</v>
@@ -3046,13 +5589,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="D11" t="s">
         <v>19</v>
@@ -3066,13 +5609,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
@@ -3086,13 +5629,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="D13" t="s">
         <v>19</v>
@@ -3106,13 +5649,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>217</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
@@ -3126,13 +5669,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c r="B15" t="s">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>218</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
@@ -3146,13 +5689,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="C16" t="s">
-        <v>172</v>
+        <v>220</v>
       </c>
       <c r="D16" t="s">
         <v>19</v>
@@ -3166,13 +5709,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="C17" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
@@ -3186,16 +5729,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -3221,39 +5764,39 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -3261,7 +5804,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -3269,23 +5812,23 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -3293,7 +5836,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>

--- a/apps/web/public/examples/example-schedule.xlsx
+++ b/apps/web/public/examples/example-schedule.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="239">
   <si>
     <t>Term</t>
   </si>
@@ -706,7 +706,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>10:29:00</t>
+    <t>22:57:56</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -725,6 +725,9 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Default Department</t>
   </si>
   <si>
     <t>Version</t>
@@ -5755,7 +5758,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -5842,6 +5845,14 @@
         <v>19</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/apps/web/public/examples/example-schedule.xlsx
+++ b/apps/web/public/examples/example-schedule.xlsx
@@ -124,10 +124,10 @@
     <t>Advising coordinator</t>
   </si>
   <si>
-    <t>DATA</t>
-  </si>
-  <si>
-    <t>202</t>
+    <t>AMUS</t>
+  </si>
+  <si>
+    <t>112</t>
   </si>
   <si>
     <t>A</t>
@@ -136,264 +136,264 @@
     <t>4</t>
   </si>
   <si>
+    <t>MWF</t>
+  </si>
+  <si>
+    <t>09:15:00 - 10:20:00</t>
+  </si>
+  <si>
+    <t>NH 101</t>
+  </si>
+  <si>
+    <t>Musical Patterns I</t>
+  </si>
+  <si>
+    <t>Lecture</t>
+  </si>
+  <si>
+    <t>In-Person</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>MTWRF</t>
+  </si>
+  <si>
+    <t>09:00:00 - 11:30:00</t>
+  </si>
+  <si>
+    <t>Second</t>
+  </si>
+  <si>
+    <t>SU-Second</t>
+  </si>
+  <si>
+    <t>Summer session II</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>11:00:00 - 12:05:00</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Musical Patterns I (second semester)</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:20:00</t>
+  </si>
+  <si>
+    <t>NH 102</t>
+  </si>
+  <si>
+    <t>Musical Patterns II</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>WI-Full</t>
+  </si>
+  <si>
+    <t>Algorithms and Music</t>
+  </si>
+  <si>
+    <t>Cy Fictional</t>
+  </si>
+  <si>
+    <t>Winter intensive: meets every weekday for two weeks</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:05:00</t>
+  </si>
+  <si>
+    <t>NH 103</t>
+  </si>
+  <si>
+    <t>Discrete Rhythm</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
     <t>TR</t>
   </si>
   <si>
+    <t>10:20:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>Harmonic Structures</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>Multivoice Analysis</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>14:10:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>NH 104</t>
+  </si>
+  <si>
+    <t>Corpus Studies I</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Corpus Studies II</t>
+  </si>
+  <si>
+    <t>BHAV</t>
+  </si>
+  <si>
+    <t>13:30:00 - 14:35:00</t>
+  </si>
+  <si>
+    <t>NH 105</t>
+  </si>
+  <si>
+    <t>Introduction to Behavioral Dynamics</t>
+  </si>
+  <si>
+    <t>Dee Placeholder</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>SU-First</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Summer session I</t>
+  </si>
+  <si>
+    <t>14:45:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>13:00:00 - 15:30:00</t>
+  </si>
+  <si>
+    <t>Behavior in Sport</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:55:00</t>
+  </si>
+  <si>
+    <t>Stochastic Behavior</t>
+  </si>
+  <si>
+    <t>Eli Specimen, Dee Placeholder</t>
+  </si>
+  <si>
+    <t>DIGI</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
     <t>08:00:00 - 09:40:00</t>
   </si>
   <si>
     <t>SB 110</t>
   </si>
   <si>
-    <t>Data Computing</t>
+    <t>Information Computing</t>
   </si>
   <si>
     <t>Fay Mockson</t>
   </si>
   <si>
-    <t>Lecture</t>
-  </si>
-  <si>
-    <t>In-Person</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>MWF</t>
-  </si>
-  <si>
-    <t>11:00:00 - 12:05:00</t>
-  </si>
-  <si>
-    <t>Machine Learning</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:55:00</t>
-  </si>
-  <si>
-    <t>Data Science Capstone</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>14:10:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>First</t>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Network Optimization</t>
+  </si>
+  <si>
+    <t>Also listed as BHAV 306</t>
+  </si>
+  <si>
+    <t>BHAV 306</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>Adaptive Systems</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>Information Capstone</t>
+  </si>
+  <si>
+    <t>371</t>
   </si>
   <si>
     <t>FA-First</t>
   </si>
   <si>
-    <t>Data Ethics</t>
+    <t>Information Ethics</t>
   </si>
   <si>
     <t>First half of the term</t>
   </si>
   <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t>Second</t>
+    <t>378</t>
   </si>
   <si>
     <t>FA-Second</t>
   </si>
   <si>
-    <t>Data Visualization</t>
+    <t>Information Visualization</t>
   </si>
   <si>
     <t>Second half of the term</t>
   </si>
   <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>Optimization</t>
-  </si>
-  <si>
-    <t>Also listed as STAT 385</t>
-  </si>
-  <si>
-    <t>STAT 385</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>MATH</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>MTWRF</t>
-  </si>
-  <si>
-    <t>09:00:00 - 11:30:00</t>
-  </si>
-  <si>
-    <t>NH 101</t>
-  </si>
-  <si>
-    <t>WI-Full</t>
-  </si>
-  <si>
-    <t>Mathematics and Music</t>
-  </si>
-  <si>
-    <t>Cy Fictional</t>
-  </si>
-  <si>
-    <t>Winter intensive: meets every weekday for two weeks</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>09:15:00 - 10:20:00</t>
-  </si>
-  <si>
-    <t>Calculus I</t>
-  </si>
-  <si>
-    <t>SU</t>
-  </si>
-  <si>
-    <t>SU-Second</t>
-  </si>
-  <si>
-    <t>Summer session II</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>Calculus I (second semester)</t>
-  </si>
-  <si>
-    <t>162</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:20:00</t>
-  </si>
-  <si>
-    <t>NH 102</t>
-  </si>
-  <si>
-    <t>Calculus II</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>10:20:00 - 12:00:00</t>
-  </si>
-  <si>
-    <t>NH 103</t>
-  </si>
-  <si>
-    <t>Linear Algebra</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>Multivariable Calculus</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:05:00</t>
-  </si>
-  <si>
-    <t>Discrete Mathematics</t>
-  </si>
-  <si>
-    <t>351</t>
-  </si>
-  <si>
-    <t>NH 104</t>
-  </si>
-  <si>
-    <t>Real Analysis I</t>
-  </si>
-  <si>
-    <t>352</t>
-  </si>
-  <si>
-    <t>Real Analysis II</t>
-  </si>
-  <si>
-    <t>STAT</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>13:00:00 - 15:30:00</t>
-  </si>
-  <si>
-    <t>NH 105</t>
-  </si>
-  <si>
-    <t>Sports Analytics</t>
-  </si>
-  <si>
-    <t>13:30:00 - 14:35:00</t>
-  </si>
-  <si>
-    <t>Introduction to Statistics</t>
-  </si>
-  <si>
-    <t>Dee Placeholder</t>
-  </si>
-  <si>
-    <t>SU-First</t>
-  </si>
-  <si>
-    <t>Online</t>
-  </si>
-  <si>
-    <t>Summer session I</t>
-  </si>
-  <si>
-    <t>14:45:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>243</t>
-  </si>
-  <si>
-    <t>Statistical Methods</t>
-  </si>
-  <si>
-    <t>244</t>
-  </si>
-  <si>
-    <t>Regression</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>Eli Specimen, Dee Placeholder</t>
-  </si>
-  <si>
     <t>SectionId</t>
   </si>
   <si>
@@ -430,7 +430,7 @@
     <t>EnrollmentDay10</t>
   </si>
   <si>
-    <t>AY25-FA-MATH143-A</t>
+    <t>AY25-FA-AMUS112-A</t>
   </si>
   <si>
     <t>AY25</t>
@@ -439,106 +439,106 @@
     <t>09:15</t>
   </si>
   <si>
-    <t>AY25-FA-MATH143-B</t>
+    <t>AY25-FA-AMUS112-B</t>
   </si>
   <si>
     <t>11:00</t>
   </si>
   <si>
-    <t>AY25-FA-MATH162-A</t>
+    <t>AY25-FA-AMUS145-A</t>
   </si>
   <si>
     <t>12:15</t>
   </si>
   <si>
-    <t>AY25-FA-MATH231-A</t>
+    <t>AY25-FA-AMUS228-A</t>
   </si>
   <si>
     <t>10:20</t>
   </si>
   <si>
-    <t>AY25-FA-MATH256-A</t>
+    <t>AY25-FA-AMUS203-A</t>
   </si>
   <si>
     <t>08:00</t>
   </si>
   <si>
-    <t>AY25-FA-MATH351-A</t>
+    <t>AY25-FA-AMUS368-A</t>
   </si>
   <si>
     <t>14:10</t>
   </si>
   <si>
-    <t>AY25-FA-STAT143-A</t>
+    <t>AY25-FA-BHAV112-A</t>
   </si>
   <si>
     <t>13:30</t>
   </si>
   <si>
-    <t>AY25-FA-STAT143-B</t>
+    <t>AY25-FA-BHAV112-B</t>
   </si>
   <si>
     <t>14:45</t>
   </si>
   <si>
-    <t>AY25-FA-STAT243-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-STAT343-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DATA202-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DATA380-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DATA381-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DATA385-A</t>
-  </si>
-  <si>
-    <t>AY25-WI-MATH110-A</t>
+    <t>AY25-FA-BHAV212-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV312-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI225-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI371-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI378-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI306-A</t>
+  </si>
+  <si>
+    <t>AY25-WI-AMUS181-A</t>
   </si>
   <si>
     <t>09:00</t>
   </si>
   <si>
-    <t>AY25-WI-STAT130-A</t>
+    <t>AY25-WI-BHAV121-A</t>
   </si>
   <si>
     <t>13:00</t>
   </si>
   <si>
-    <t>AY25-SP-MATH144-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-MATH162-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-MATH232-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-MATH352-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-STAT143-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-STAT244-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DATA301-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DATA302-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-MATH143-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-STAT143-A</t>
+    <t>AY25-SP-AMUS119-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS145-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS235-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS375-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV112-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV219-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI318-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI325-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-AMUS112-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-BHAV112-A</t>
   </si>
   <si>
     <t>Activity</t>
@@ -700,13 +700,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-03</t>
+    <t>2026-10-04</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>22:57:56</t>
+    <t>08:26:04</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -1127,7 +1127,7 @@
     <col min="10" max="10" width="10" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="13" max="13" width="38" customWidth="1"/>
     <col min="14" max="14" width="31" customWidth="1"/>
     <col min="15" max="15" width="22" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
@@ -1506,19 +1506,19 @@
         <v>23</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M7" t="s">
         <v>42</v>
       </c>
       <c r="N7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" t="s">
         <v>43</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>44</v>
-      </c>
-      <c r="P7" t="s">
-        <v>45</v>
       </c>
       <c r="Q7" t="s">
         <v>19</v>
@@ -1529,22 +1529,22 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
         <v>47</v>
@@ -1556,28 +1556,28 @@
         <v>41</v>
       </c>
       <c r="J8" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="K8" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="L8">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="M8" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" t="s">
         <v>43</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>44</v>
       </c>
-      <c r="P8" t="s">
-        <v>45</v>
-      </c>
       <c r="Q8" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="R8" t="s">
         <v>19</v>
@@ -1585,16 +1585,16 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
         <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -1606,7 +1606,7 @@
         <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I9" t="s">
         <v>41</v>
@@ -1615,22 +1615,22 @@
         <v>22</v>
       </c>
       <c r="K9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M9" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="N9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" t="s">
         <v>43</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>44</v>
-      </c>
-      <c r="P9" t="s">
-        <v>45</v>
       </c>
       <c r="Q9" t="s">
         <v>19</v>
@@ -1641,55 +1641,55 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
         <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
         <v>39</v>
       </c>
       <c r="H10" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s">
         <v>41</v>
       </c>
       <c r="J10" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="K10" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" t="s">
         <v>43</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>44</v>
       </c>
-      <c r="P10" t="s">
-        <v>45</v>
-      </c>
       <c r="Q10" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="R10" t="s">
         <v>19</v>
@@ -1703,49 +1703,49 @@
         <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
         <v>37</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
         <v>39</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I11" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="J11" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="K11" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="N11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" t="s">
         <v>43</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>44</v>
       </c>
-      <c r="P11" t="s">
-        <v>45</v>
-      </c>
       <c r="Q11" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="R11" t="s">
         <v>19</v>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
         <v>37</v>
@@ -1771,51 +1771,51 @@
         <v>38</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
       </c>
       <c r="K12" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L12">
         <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="N12" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" t="s">
         <v>43</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>44</v>
       </c>
-      <c r="P12" t="s">
-        <v>45</v>
-      </c>
       <c r="Q12" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="R12" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
         <v>37</v>
@@ -1827,37 +1827,37 @@
         <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="J13" t="s">
         <v>22</v>
       </c>
       <c r="K13" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="L13">
         <v>150</v>
       </c>
       <c r="M13" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="N13" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="O13" t="s">
+        <v>43</v>
+      </c>
+      <c r="P13" t="s">
         <v>44</v>
       </c>
-      <c r="P13" t="s">
-        <v>45</v>
-      </c>
       <c r="Q13" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="R13" t="s">
         <v>19</v>
@@ -1868,10 +1868,10 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
         <v>37</v>
@@ -1883,13 +1883,13 @@
         <v>38</v>
       </c>
       <c r="G14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="I14" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J14" t="s">
         <v>22</v>
@@ -1901,16 +1901,16 @@
         <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="N14" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="O14" t="s">
+        <v>43</v>
+      </c>
+      <c r="P14" t="s">
         <v>44</v>
-      </c>
-      <c r="P14" t="s">
-        <v>45</v>
       </c>
       <c r="Q14" t="s">
         <v>19</v>
@@ -1921,55 +1921,55 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
         <v>70</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
       </c>
       <c r="D15" t="s">
         <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" t="s">
         <v>72</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15">
+        <v>100</v>
+      </c>
+      <c r="M15" t="s">
         <v>73</v>
       </c>
-      <c r="I15" t="s">
-        <v>74</v>
-      </c>
-      <c r="J15" t="s">
-        <v>61</v>
-      </c>
-      <c r="K15" t="s">
-        <v>83</v>
-      </c>
-      <c r="L15">
-        <v>150</v>
-      </c>
-      <c r="M15" t="s">
-        <v>81</v>
-      </c>
       <c r="N15" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="O15" t="s">
+        <v>43</v>
+      </c>
+      <c r="P15" t="s">
         <v>44</v>
       </c>
-      <c r="P15" t="s">
-        <v>45</v>
-      </c>
       <c r="Q15" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="R15" t="s">
         <v>19</v>
@@ -1977,16 +1977,16 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
         <v>38</v>
@@ -1995,34 +1995,34 @@
         <v>38</v>
       </c>
       <c r="G16" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="I16" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J16" t="s">
         <v>22</v>
       </c>
       <c r="K16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L16">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="N16" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="O16" t="s">
+        <v>43</v>
+      </c>
+      <c r="P16" t="s">
         <v>44</v>
-      </c>
-      <c r="P16" t="s">
-        <v>45</v>
       </c>
       <c r="Q16" t="s">
         <v>19</v>
@@ -2033,13 +2033,13 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
         <v>37</v>
@@ -2051,34 +2051,34 @@
         <v>38</v>
       </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="H17" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J17" t="s">
         <v>22</v>
       </c>
       <c r="K17" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L17">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M17" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="N17" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O17" t="s">
+        <v>43</v>
+      </c>
+      <c r="P17" t="s">
         <v>44</v>
-      </c>
-      <c r="P17" t="s">
-        <v>45</v>
       </c>
       <c r="Q17" t="s">
         <v>19</v>
@@ -2089,13 +2089,13 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>37</v>
@@ -2107,34 +2107,34 @@
         <v>38</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="H18" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I18" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J18" t="s">
         <v>22</v>
       </c>
       <c r="K18" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L18">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="N18" t="s">
         <v>30</v>
       </c>
       <c r="O18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P18" t="s">
         <v>44</v>
-      </c>
-      <c r="P18" t="s">
-        <v>45</v>
       </c>
       <c r="Q18" t="s">
         <v>19</v>
@@ -2145,13 +2145,13 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
         <v>37</v>
@@ -2163,34 +2163,34 @@
         <v>38</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="J19" t="s">
         <v>22</v>
       </c>
       <c r="K19" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L19">
         <v>65</v>
       </c>
       <c r="M19" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="N19" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="O19" t="s">
+        <v>43</v>
+      </c>
+      <c r="P19" t="s">
         <v>44</v>
-      </c>
-      <c r="P19" t="s">
-        <v>45</v>
       </c>
       <c r="Q19" t="s">
         <v>19</v>
@@ -2201,13 +2201,13 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
         <v>37</v>
@@ -2222,31 +2222,31 @@
         <v>39</v>
       </c>
       <c r="H20" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I20" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J20" t="s">
         <v>22</v>
       </c>
       <c r="K20" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="M20" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="N20" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="O20" t="s">
+        <v>43</v>
+      </c>
+      <c r="P20" t="s">
         <v>44</v>
-      </c>
-      <c r="P20" t="s">
-        <v>45</v>
       </c>
       <c r="Q20" t="s">
         <v>19</v>
@@ -2257,55 +2257,55 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
         <v>37</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H21" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J21" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M21" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="N21" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="O21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P21" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="Q21" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="R21" t="s">
         <v>19</v>
@@ -2316,13 +2316,13 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E22" t="s">
         <v>38</v>
@@ -2331,13 +2331,13 @@
         <v>38</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H22" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
         <v>22</v>
@@ -2349,16 +2349,16 @@
         <v>65</v>
       </c>
       <c r="M22" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="N22" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="O22" t="s">
+        <v>43</v>
+      </c>
+      <c r="P22" t="s">
         <v>44</v>
-      </c>
-      <c r="P22" t="s">
-        <v>45</v>
       </c>
       <c r="Q22" t="s">
         <v>19</v>
@@ -2369,13 +2369,13 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
         <v>37</v>
@@ -2387,34 +2387,34 @@
         <v>38</v>
       </c>
       <c r="G23" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H23" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="I23" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="J23" t="s">
         <v>22</v>
       </c>
       <c r="K23" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M23" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="N23" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O23" t="s">
+        <v>43</v>
+      </c>
+      <c r="P23" t="s">
         <v>44</v>
-      </c>
-      <c r="P23" t="s">
-        <v>45</v>
       </c>
       <c r="Q23" t="s">
         <v>19</v>
@@ -2425,13 +2425,13 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
         <v>37</v>
@@ -2443,34 +2443,34 @@
         <v>38</v>
       </c>
       <c r="G24" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="H24" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="I24" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="J24" t="s">
         <v>22</v>
       </c>
       <c r="K24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="N24" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O24" t="s">
+        <v>43</v>
+      </c>
+      <c r="P24" t="s">
         <v>44</v>
-      </c>
-      <c r="P24" t="s">
-        <v>45</v>
       </c>
       <c r="Q24" t="s">
         <v>19</v>
@@ -2481,13 +2481,13 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s">
         <v>37</v>
@@ -2499,34 +2499,34 @@
         <v>38</v>
       </c>
       <c r="G25" t="s">
+        <v>71</v>
+      </c>
+      <c r="H25" t="s">
         <v>72</v>
       </c>
-      <c r="H25" t="s">
-        <v>108</v>
-      </c>
       <c r="I25" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="J25" t="s">
         <v>22</v>
       </c>
       <c r="K25" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="L25">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="N25" t="s">
         <v>33</v>
       </c>
       <c r="O25" t="s">
+        <v>43</v>
+      </c>
+      <c r="P25" t="s">
         <v>44</v>
-      </c>
-      <c r="P25" t="s">
-        <v>45</v>
       </c>
       <c r="Q25" t="s">
         <v>19</v>
@@ -2540,10 +2540,10 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
         <v>37</v>
@@ -2555,13 +2555,13 @@
         <v>38</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="H26" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I26" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="J26" t="s">
         <v>22</v>
@@ -2570,19 +2570,19 @@
         <v>23</v>
       </c>
       <c r="L26">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M26" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="N26" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="O26" t="s">
+        <v>43</v>
+      </c>
+      <c r="P26" t="s">
         <v>44</v>
-      </c>
-      <c r="P26" t="s">
-        <v>45</v>
       </c>
       <c r="Q26" t="s">
         <v>19</v>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
         <v>37</v>
@@ -2611,34 +2611,34 @@
         <v>38</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="H27" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I27" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J27" t="s">
         <v>22</v>
       </c>
       <c r="K27" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="L27">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="M27" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="N27" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="O27" t="s">
+        <v>43</v>
+      </c>
+      <c r="P27" t="s">
         <v>44</v>
-      </c>
-      <c r="P27" t="s">
-        <v>45</v>
       </c>
       <c r="Q27" t="s">
         <v>19</v>
@@ -2649,72 +2649,72 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>37</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G28" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="H28" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="I28" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J28" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="K28" t="s">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="L28">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="M28" t="s">
+        <v>110</v>
+      </c>
+      <c r="N28" t="s">
+        <v>108</v>
+      </c>
+      <c r="O28" t="s">
+        <v>43</v>
+      </c>
+      <c r="P28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>111</v>
+      </c>
+      <c r="R28" t="s">
         <v>112</v>
-      </c>
-      <c r="N28" t="s">
-        <v>113</v>
-      </c>
-      <c r="O28" t="s">
-        <v>44</v>
-      </c>
-      <c r="P28" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>116</v>
-      </c>
-      <c r="R28" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="E29" t="s">
         <v>38</v>
@@ -2723,34 +2723,34 @@
         <v>38</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H29" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="I29" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J29" t="s">
         <v>22</v>
       </c>
       <c r="K29" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L29">
         <v>65</v>
       </c>
       <c r="M29" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N29" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="O29" t="s">
+        <v>43</v>
+      </c>
+      <c r="P29" t="s">
         <v>44</v>
-      </c>
-      <c r="P29" t="s">
-        <v>45</v>
       </c>
       <c r="Q29" t="s">
         <v>19</v>
@@ -2761,13 +2761,13 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
         <v>37</v>
@@ -2779,34 +2779,34 @@
         <v>38</v>
       </c>
       <c r="G30" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="H30" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I30" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J30" t="s">
         <v>22</v>
       </c>
       <c r="K30" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="O30" t="s">
+        <v>43</v>
+      </c>
+      <c r="P30" t="s">
         <v>44</v>
-      </c>
-      <c r="P30" t="s">
-        <v>45</v>
       </c>
       <c r="Q30" t="s">
         <v>19</v>
@@ -2817,55 +2817,55 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
         <v>37</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="H31" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="I31" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J31" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="K31" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N31" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="O31" t="s">
+        <v>43</v>
+      </c>
+      <c r="P31" t="s">
         <v>44</v>
       </c>
-      <c r="P31" t="s">
-        <v>45</v>
-      </c>
       <c r="Q31" t="s">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="R31" t="s">
         <v>19</v>
@@ -2876,34 +2876,34 @@
         <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
         <v>37</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G32" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="H32" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="I32" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J32" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="K32" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -2912,16 +2912,16 @@
         <v>123</v>
       </c>
       <c r="N32" t="s">
+        <v>108</v>
+      </c>
+      <c r="O32" t="s">
+        <v>43</v>
+      </c>
+      <c r="P32" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q32" t="s">
         <v>124</v>
-      </c>
-      <c r="O32" t="s">
-        <v>44</v>
-      </c>
-      <c r="P32" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>19</v>
       </c>
       <c r="R32" t="s">
         <v>19</v>
@@ -2952,7 +2952,7 @@
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="30" customWidth="1"/>
+    <col min="17" max="17" width="38" customWidth="1"/>
     <col min="18" max="18" width="21" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="7" customWidth="1"/>
@@ -3053,10 +3053,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
         <v>37</v>
@@ -3074,7 +3074,7 @@
         <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N2" t="s">
         <v>139</v>
@@ -3083,22 +3083,22 @@
         <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U2" t="s">
         <v>44</v>
-      </c>
-      <c r="S2" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" t="s">
-        <v>19</v>
-      </c>
-      <c r="U2" t="s">
-        <v>45</v>
       </c>
       <c r="V2" t="s">
         <v>19</v>
@@ -3127,13 +3127,13 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="I3" t="s">
         <v>24</v>
@@ -3148,7 +3148,7 @@
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N3" t="s">
         <v>141</v>
@@ -3157,22 +3157,22 @@
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="R3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U3" t="s">
         <v>44</v>
-      </c>
-      <c r="S3" t="s">
-        <v>19</v>
-      </c>
-      <c r="T3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U3" t="s">
-        <v>45</v>
       </c>
       <c r="V3" t="s">
         <v>19</v>
@@ -3201,10 +3201,10 @@
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="H4" t="s">
         <v>37</v>
@@ -3222,7 +3222,7 @@
         <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N4" t="s">
         <v>143</v>
@@ -3231,22 +3231,22 @@
         <v>65</v>
       </c>
       <c r="P4" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="Q4" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="R4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" t="s">
+        <v>19</v>
+      </c>
+      <c r="T4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U4" t="s">
         <v>44</v>
-      </c>
-      <c r="S4" t="s">
-        <v>19</v>
-      </c>
-      <c r="T4" t="s">
-        <v>19</v>
-      </c>
-      <c r="U4" t="s">
-        <v>45</v>
       </c>
       <c r="V4" t="s">
         <v>19</v>
@@ -3275,16 +3275,16 @@
         <v>22</v>
       </c>
       <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
         <v>70</v>
-      </c>
-      <c r="G5" t="s">
-        <v>92</v>
       </c>
       <c r="H5" t="s">
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -3296,7 +3296,7 @@
         <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="N5" t="s">
         <v>145</v>
@@ -3305,22 +3305,22 @@
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="Q5" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="R5" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" t="s">
+        <v>19</v>
+      </c>
+      <c r="T5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U5" t="s">
         <v>44</v>
-      </c>
-      <c r="S5" t="s">
-        <v>19</v>
-      </c>
-      <c r="T5" t="s">
-        <v>19</v>
-      </c>
-      <c r="U5" t="s">
-        <v>45</v>
       </c>
       <c r="V5" t="s">
         <v>19</v>
@@ -3349,16 +3349,16 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
         <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3370,7 +3370,7 @@
         <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N6" t="s">
         <v>147</v>
@@ -3379,22 +3379,22 @@
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="Q6" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="R6" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" t="s">
+        <v>19</v>
+      </c>
+      <c r="T6" t="s">
+        <v>19</v>
+      </c>
+      <c r="U6" t="s">
         <v>44</v>
-      </c>
-      <c r="S6" t="s">
-        <v>19</v>
-      </c>
-      <c r="T6" t="s">
-        <v>19</v>
-      </c>
-      <c r="U6" t="s">
-        <v>45</v>
       </c>
       <c r="V6" t="s">
         <v>19</v>
@@ -3423,10 +3423,10 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="H7" t="s">
         <v>37</v>
@@ -3444,7 +3444,7 @@
         <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="N7" t="s">
         <v>149</v>
@@ -3453,22 +3453,22 @@
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="Q7" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="R7" t="s">
+        <v>43</v>
+      </c>
+      <c r="S7" t="s">
+        <v>19</v>
+      </c>
+      <c r="T7" t="s">
+        <v>19</v>
+      </c>
+      <c r="U7" t="s">
         <v>44</v>
-      </c>
-      <c r="S7" t="s">
-        <v>19</v>
-      </c>
-      <c r="T7" t="s">
-        <v>19</v>
-      </c>
-      <c r="U7" t="s">
-        <v>45</v>
       </c>
       <c r="V7" t="s">
         <v>19</v>
@@ -3497,16 +3497,16 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
         <v>37</v>
       </c>
       <c r="I8" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3518,7 +3518,7 @@
         <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N8" t="s">
         <v>151</v>
@@ -3527,22 +3527,22 @@
         <v>65</v>
       </c>
       <c r="P8" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="Q8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="R8" t="s">
+        <v>43</v>
+      </c>
+      <c r="S8" t="s">
+        <v>19</v>
+      </c>
+      <c r="T8" t="s">
+        <v>19</v>
+      </c>
+      <c r="U8" t="s">
         <v>44</v>
-      </c>
-      <c r="S8" t="s">
-        <v>19</v>
-      </c>
-      <c r="T8" t="s">
-        <v>19</v>
-      </c>
-      <c r="U8" t="s">
-        <v>45</v>
       </c>
       <c r="V8" t="s">
         <v>19</v>
@@ -3571,16 +3571,16 @@
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G9" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -3592,7 +3592,7 @@
         <v>19</v>
       </c>
       <c r="M9" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N9" t="s">
         <v>153</v>
@@ -3601,22 +3601,22 @@
         <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="Q9" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="R9" t="s">
+        <v>43</v>
+      </c>
+      <c r="S9" t="s">
+        <v>19</v>
+      </c>
+      <c r="T9" t="s">
+        <v>19</v>
+      </c>
+      <c r="U9" t="s">
         <v>44</v>
-      </c>
-      <c r="S9" t="s">
-        <v>19</v>
-      </c>
-      <c r="T9" t="s">
-        <v>19</v>
-      </c>
-      <c r="U9" t="s">
-        <v>45</v>
       </c>
       <c r="V9" t="s">
         <v>19</v>
@@ -3645,10 +3645,10 @@
         <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="H10" t="s">
         <v>37</v>
@@ -3666,7 +3666,7 @@
         <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="N10" t="s">
         <v>145</v>
@@ -3675,22 +3675,22 @@
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="Q10" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="R10" t="s">
+        <v>43</v>
+      </c>
+      <c r="S10" t="s">
+        <v>19</v>
+      </c>
+      <c r="T10" t="s">
+        <v>19</v>
+      </c>
+      <c r="U10" t="s">
         <v>44</v>
-      </c>
-      <c r="S10" t="s">
-        <v>19</v>
-      </c>
-      <c r="T10" t="s">
-        <v>19</v>
-      </c>
-      <c r="U10" t="s">
-        <v>45</v>
       </c>
       <c r="V10" t="s">
         <v>19</v>
@@ -3719,16 +3719,16 @@
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G11" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="H11" t="s">
         <v>37</v>
       </c>
       <c r="I11" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3740,7 +3740,7 @@
         <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="N11" t="s">
         <v>143</v>
@@ -3749,22 +3749,22 @@
         <v>100</v>
       </c>
       <c r="P11" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="Q11" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="R11" t="s">
+        <v>43</v>
+      </c>
+      <c r="S11" t="s">
+        <v>19</v>
+      </c>
+      <c r="T11" t="s">
+        <v>19</v>
+      </c>
+      <c r="U11" t="s">
         <v>44</v>
-      </c>
-      <c r="S11" t="s">
-        <v>19</v>
-      </c>
-      <c r="T11" t="s">
-        <v>19</v>
-      </c>
-      <c r="U11" t="s">
-        <v>45</v>
       </c>
       <c r="V11" t="s">
         <v>19</v>
@@ -3793,16 +3793,16 @@
         <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="H12" t="s">
         <v>37</v>
       </c>
       <c r="I12" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -3814,7 +3814,7 @@
         <v>19</v>
       </c>
       <c r="M12" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="N12" t="s">
         <v>147</v>
@@ -3823,22 +3823,22 @@
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="Q12" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="R12" t="s">
+        <v>43</v>
+      </c>
+      <c r="S12" t="s">
+        <v>19</v>
+      </c>
+      <c r="T12" t="s">
+        <v>19</v>
+      </c>
+      <c r="U12" t="s">
         <v>44</v>
-      </c>
-      <c r="S12" t="s">
-        <v>19</v>
-      </c>
-      <c r="T12" t="s">
-        <v>19</v>
-      </c>
-      <c r="U12" t="s">
-        <v>45</v>
       </c>
       <c r="V12" t="s">
         <v>19</v>
@@ -3864,19 +3864,19 @@
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="H13" t="s">
         <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -3888,7 +3888,7 @@
         <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="N13" t="s">
         <v>149</v>
@@ -3897,25 +3897,25 @@
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="Q13" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="R13" t="s">
+        <v>43</v>
+      </c>
+      <c r="S13" t="s">
+        <v>19</v>
+      </c>
+      <c r="T13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U13" t="s">
         <v>44</v>
       </c>
-      <c r="S13" t="s">
-        <v>19</v>
-      </c>
-      <c r="T13" t="s">
-        <v>19</v>
-      </c>
-      <c r="U13" t="s">
-        <v>45</v>
-      </c>
       <c r="V13" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="W13" t="s">
         <v>19</v>
@@ -3938,19 +3938,19 @@
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="H14" t="s">
         <v>37</v>
       </c>
       <c r="I14" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -3962,7 +3962,7 @@
         <v>19</v>
       </c>
       <c r="M14" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="N14" t="s">
         <v>149</v>
@@ -3971,25 +3971,25 @@
         <v>100</v>
       </c>
       <c r="P14" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="Q14" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="R14" t="s">
+        <v>43</v>
+      </c>
+      <c r="S14" t="s">
+        <v>19</v>
+      </c>
+      <c r="T14" t="s">
+        <v>19</v>
+      </c>
+      <c r="U14" t="s">
         <v>44</v>
       </c>
-      <c r="S14" t="s">
-        <v>19</v>
-      </c>
-      <c r="T14" t="s">
-        <v>19</v>
-      </c>
-      <c r="U14" t="s">
-        <v>45</v>
-      </c>
       <c r="V14" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="W14" t="s">
         <v>19</v>
@@ -4015,16 +4015,16 @@
         <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="H15" t="s">
         <v>37</v>
       </c>
       <c r="I15" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4036,7 +4036,7 @@
         <v>19</v>
       </c>
       <c r="M15" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N15" t="s">
         <v>141</v>
@@ -4045,25 +4045,25 @@
         <v>65</v>
       </c>
       <c r="P15" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="Q15" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="R15" t="s">
+        <v>43</v>
+      </c>
+      <c r="S15" t="s">
+        <v>19</v>
+      </c>
+      <c r="T15" t="s">
+        <v>19</v>
+      </c>
+      <c r="U15" t="s">
         <v>44</v>
       </c>
-      <c r="S15" t="s">
-        <v>19</v>
-      </c>
-      <c r="T15" t="s">
-        <v>19</v>
-      </c>
-      <c r="U15" t="s">
-        <v>45</v>
-      </c>
       <c r="V15" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="W15" t="s">
         <v>19</v>
@@ -4083,22 +4083,22 @@
         <v>138</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H16" t="s">
         <v>37</v>
       </c>
       <c r="I16" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -4110,7 +4110,7 @@
         <v>19</v>
       </c>
       <c r="M16" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="N16" t="s">
         <v>161</v>
@@ -4119,25 +4119,25 @@
         <v>150</v>
       </c>
       <c r="P16" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q16" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="R16" t="s">
+        <v>43</v>
+      </c>
+      <c r="S16" t="s">
+        <v>19</v>
+      </c>
+      <c r="T16" t="s">
+        <v>19</v>
+      </c>
+      <c r="U16" t="s">
         <v>44</v>
       </c>
-      <c r="S16" t="s">
-        <v>19</v>
-      </c>
-      <c r="T16" t="s">
-        <v>19</v>
-      </c>
-      <c r="U16" t="s">
-        <v>45</v>
-      </c>
       <c r="V16" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="W16" t="s">
         <v>19</v>
@@ -4157,16 +4157,16 @@
         <v>138</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="H17" t="s">
         <v>37</v>
@@ -4184,7 +4184,7 @@
         <v>19</v>
       </c>
       <c r="M17" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="N17" t="s">
         <v>163</v>
@@ -4193,22 +4193,22 @@
         <v>150</v>
       </c>
       <c r="P17" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="Q17" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="R17" t="s">
+        <v>43</v>
+      </c>
+      <c r="S17" t="s">
+        <v>19</v>
+      </c>
+      <c r="T17" t="s">
+        <v>19</v>
+      </c>
+      <c r="U17" t="s">
         <v>44</v>
-      </c>
-      <c r="S17" t="s">
-        <v>19</v>
-      </c>
-      <c r="T17" t="s">
-        <v>19</v>
-      </c>
-      <c r="U17" t="s">
-        <v>45</v>
       </c>
       <c r="V17" t="s">
         <v>19</v>
@@ -4237,10 +4237,10 @@
         <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="H18" t="s">
         <v>37</v>
@@ -4258,7 +4258,7 @@
         <v>19</v>
       </c>
       <c r="M18" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N18" t="s">
         <v>139</v>
@@ -4267,22 +4267,22 @@
         <v>65</v>
       </c>
       <c r="P18" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q18" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="R18" t="s">
+        <v>43</v>
+      </c>
+      <c r="S18" t="s">
+        <v>19</v>
+      </c>
+      <c r="T18" t="s">
+        <v>19</v>
+      </c>
+      <c r="U18" t="s">
         <v>44</v>
-      </c>
-      <c r="S18" t="s">
-        <v>19</v>
-      </c>
-      <c r="T18" t="s">
-        <v>19</v>
-      </c>
-      <c r="U18" t="s">
-        <v>45</v>
       </c>
       <c r="V18" t="s">
         <v>19</v>
@@ -4311,10 +4311,10 @@
         <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="H19" t="s">
         <v>37</v>
@@ -4332,7 +4332,7 @@
         <v>19</v>
       </c>
       <c r="M19" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N19" t="s">
         <v>139</v>
@@ -4341,22 +4341,22 @@
         <v>65</v>
       </c>
       <c r="P19" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="Q19" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="R19" t="s">
+        <v>43</v>
+      </c>
+      <c r="S19" t="s">
+        <v>19</v>
+      </c>
+      <c r="T19" t="s">
+        <v>19</v>
+      </c>
+      <c r="U19" t="s">
         <v>44</v>
-      </c>
-      <c r="S19" t="s">
-        <v>19</v>
-      </c>
-      <c r="T19" t="s">
-        <v>19</v>
-      </c>
-      <c r="U19" t="s">
-        <v>45</v>
       </c>
       <c r="V19" t="s">
         <v>19</v>
@@ -4385,16 +4385,16 @@
         <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G20" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="H20" t="s">
         <v>37</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -4406,7 +4406,7 @@
         <v>19</v>
       </c>
       <c r="M20" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="N20" t="s">
         <v>145</v>
@@ -4415,22 +4415,22 @@
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="Q20" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R20" t="s">
+        <v>43</v>
+      </c>
+      <c r="S20" t="s">
+        <v>19</v>
+      </c>
+      <c r="T20" t="s">
+        <v>19</v>
+      </c>
+      <c r="U20" t="s">
         <v>44</v>
-      </c>
-      <c r="S20" t="s">
-        <v>19</v>
-      </c>
-      <c r="T20" t="s">
-        <v>19</v>
-      </c>
-      <c r="U20" t="s">
-        <v>45</v>
       </c>
       <c r="V20" t="s">
         <v>19</v>
@@ -4459,10 +4459,10 @@
         <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G21" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s">
         <v>37</v>
@@ -4480,7 +4480,7 @@
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="N21" t="s">
         <v>149</v>
@@ -4489,22 +4489,22 @@
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="Q21" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="R21" t="s">
+        <v>43</v>
+      </c>
+      <c r="S21" t="s">
+        <v>19</v>
+      </c>
+      <c r="T21" t="s">
+        <v>19</v>
+      </c>
+      <c r="U21" t="s">
         <v>44</v>
-      </c>
-      <c r="S21" t="s">
-        <v>19</v>
-      </c>
-      <c r="T21" t="s">
-        <v>19</v>
-      </c>
-      <c r="U21" t="s">
-        <v>45</v>
       </c>
       <c r="V21" t="s">
         <v>19</v>
@@ -4533,16 +4533,16 @@
         <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H22" t="s">
         <v>37</v>
       </c>
       <c r="I22" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -4554,7 +4554,7 @@
         <v>19</v>
       </c>
       <c r="M22" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N22" t="s">
         <v>151</v>
@@ -4563,22 +4563,22 @@
         <v>65</v>
       </c>
       <c r="P22" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="Q22" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="R22" t="s">
+        <v>43</v>
+      </c>
+      <c r="S22" t="s">
+        <v>19</v>
+      </c>
+      <c r="T22" t="s">
+        <v>19</v>
+      </c>
+      <c r="U22" t="s">
         <v>44</v>
-      </c>
-      <c r="S22" t="s">
-        <v>19</v>
-      </c>
-      <c r="T22" t="s">
-        <v>19</v>
-      </c>
-      <c r="U22" t="s">
-        <v>45</v>
       </c>
       <c r="V22" t="s">
         <v>19</v>
@@ -4607,10 +4607,10 @@
         <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="H23" t="s">
         <v>37</v>
@@ -4628,7 +4628,7 @@
         <v>19</v>
       </c>
       <c r="M23" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="N23" t="s">
         <v>145</v>
@@ -4637,22 +4637,22 @@
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="Q23" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="R23" t="s">
+        <v>43</v>
+      </c>
+      <c r="S23" t="s">
+        <v>19</v>
+      </c>
+      <c r="T23" t="s">
+        <v>19</v>
+      </c>
+      <c r="U23" t="s">
         <v>44</v>
-      </c>
-      <c r="S23" t="s">
-        <v>19</v>
-      </c>
-      <c r="T23" t="s">
-        <v>19</v>
-      </c>
-      <c r="U23" t="s">
-        <v>45</v>
       </c>
       <c r="V23" t="s">
         <v>19</v>
@@ -4681,16 +4681,16 @@
         <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="G24" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
       <c r="H24" t="s">
         <v>37</v>
       </c>
       <c r="I24" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -4702,7 +4702,7 @@
         <v>19</v>
       </c>
       <c r="M24" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N24" t="s">
         <v>141</v>
@@ -4711,22 +4711,22 @@
         <v>65</v>
       </c>
       <c r="P24" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="Q24" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="R24" t="s">
+        <v>43</v>
+      </c>
+      <c r="S24" t="s">
+        <v>19</v>
+      </c>
+      <c r="T24" t="s">
+        <v>19</v>
+      </c>
+      <c r="U24" t="s">
         <v>44</v>
-      </c>
-      <c r="S24" t="s">
-        <v>19</v>
-      </c>
-      <c r="T24" t="s">
-        <v>19</v>
-      </c>
-      <c r="U24" t="s">
-        <v>45</v>
       </c>
       <c r="V24" t="s">
         <v>19</v>
@@ -4755,16 +4755,16 @@
         <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="G25" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="H25" t="s">
         <v>37</v>
       </c>
       <c r="I25" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="J25">
         <v>4</v>
@@ -4776,7 +4776,7 @@
         <v>19</v>
       </c>
       <c r="M25" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="N25" t="s">
         <v>143</v>
@@ -4785,22 +4785,22 @@
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="Q25" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="R25" t="s">
+        <v>43</v>
+      </c>
+      <c r="S25" t="s">
+        <v>19</v>
+      </c>
+      <c r="T25" t="s">
+        <v>19</v>
+      </c>
+      <c r="U25" t="s">
         <v>44</v>
-      </c>
-      <c r="S25" t="s">
-        <v>19</v>
-      </c>
-      <c r="T25" t="s">
-        <v>19</v>
-      </c>
-      <c r="U25" t="s">
-        <v>45</v>
       </c>
       <c r="V25" t="s">
         <v>19</v>
@@ -4823,16 +4823,16 @@
         <v>138</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="G26" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H26" t="s">
         <v>37</v>
@@ -4850,7 +4850,7 @@
         <v>19</v>
       </c>
       <c r="M26" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="N26" t="s">
         <v>161</v>
@@ -4859,25 +4859,25 @@
         <v>150</v>
       </c>
       <c r="P26" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q26" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="R26" t="s">
+        <v>43</v>
+      </c>
+      <c r="S26" t="s">
+        <v>19</v>
+      </c>
+      <c r="T26" t="s">
+        <v>19</v>
+      </c>
+      <c r="U26" t="s">
         <v>44</v>
       </c>
-      <c r="S26" t="s">
-        <v>19</v>
-      </c>
-      <c r="T26" t="s">
-        <v>19</v>
-      </c>
-      <c r="U26" t="s">
-        <v>45</v>
-      </c>
       <c r="V26" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="W26" t="s">
         <v>19</v>
@@ -4897,22 +4897,22 @@
         <v>138</v>
       </c>
       <c r="D27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27" t="s">
         <v>82</v>
       </c>
-      <c r="E27" t="s">
-        <v>56</v>
-      </c>
-      <c r="F27" t="s">
-        <v>106</v>
-      </c>
       <c r="G27" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="H27" t="s">
         <v>37</v>
       </c>
       <c r="I27" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -4924,7 +4924,7 @@
         <v>19</v>
       </c>
       <c r="M27" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="N27" t="s">
         <v>161</v>
@@ -4933,13 +4933,13 @@
         <v>150</v>
       </c>
       <c r="P27" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="Q27" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="R27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S27" t="s">
         <v>19</v>
@@ -4948,10 +4948,10 @@
         <v>19</v>
       </c>
       <c r="U27" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="V27" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="W27" t="s">
         <v>19</v>
@@ -4992,10 +4992,10 @@
         <v>159</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5290,7 +5290,7 @@
         <v>196</v>
       </c>
       <c r="N3" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="O3" t="s">
         <v>19</v>
@@ -5352,7 +5352,7 @@
         <v>196</v>
       </c>
       <c r="N4" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="O4" t="s">
         <v>19</v>
@@ -5475,7 +5475,7 @@
         <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
         <v>19</v>
@@ -5535,7 +5535,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
         <v>210</v>
@@ -5575,7 +5575,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>212</v>
@@ -5615,7 +5615,7 @@
         <v>213</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
         <v>215</v>
@@ -5635,7 +5635,7 @@
         <v>213</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
         <v>216</v>
@@ -5675,7 +5675,7 @@
         <v>213</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
         <v>218</v>
@@ -5741,7 +5741,7 @@
         <v>223</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E18">
         <v>1</v>

--- a/apps/web/public/examples/example-schedule.xlsx
+++ b/apps/web/public/examples/example-schedule.xlsx
@@ -706,7 +706,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:26:04</t>
+    <t>08:32:09</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-schedule.xlsx
+++ b/apps/web/public/examples/example-schedule.xlsx
@@ -706,7 +706,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:32:09</t>
+    <t>21:03:16</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-schedule.xlsx
+++ b/apps/web/public/examples/example-schedule.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="243">
   <si>
     <t>Term</t>
   </si>
@@ -73,6 +73,15 @@
     <t>CrossListings</t>
   </si>
   <si>
+    <t>CoreTag</t>
+  </si>
+  <si>
+    <t>SpecialTopic</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
     <t>FA</t>
   </si>
   <si>
@@ -154,6 +163,9 @@
     <t>In-Person</t>
   </si>
   <si>
+    <t>UGRAD</t>
+  </si>
+  <si>
     <t>SU</t>
   </si>
   <si>
@@ -166,507 +178,507 @@
     <t>09:00:00 - 11:30:00</t>
   </si>
   <si>
+    <t>SU-2</t>
+  </si>
+  <si>
+    <t>Summer session II</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>11:00:00 - 12:05:00</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Musical Patterns I (second semester)</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:20:00</t>
+  </si>
+  <si>
+    <t>NH 102</t>
+  </si>
+  <si>
+    <t>Musical Patterns II</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>WI-Full</t>
+  </si>
+  <si>
+    <t>Algorithms and Music</t>
+  </si>
+  <si>
+    <t>Cy Fictional</t>
+  </si>
+  <si>
+    <t>Winter intensive: meets every weekday for two weeks</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:05:00</t>
+  </si>
+  <si>
+    <t>NH 103</t>
+  </si>
+  <si>
+    <t>Discrete Rhythm</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>10:20:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>Harmonic Structures</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>Multivoice Analysis</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>14:10:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>NH 104</t>
+  </si>
+  <si>
+    <t>Corpus Studies I</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Corpus Studies II</t>
+  </si>
+  <si>
+    <t>BHAV</t>
+  </si>
+  <si>
+    <t>13:30:00 - 14:35:00</t>
+  </si>
+  <si>
+    <t>NH 105</t>
+  </si>
+  <si>
+    <t>Introduction to Behavioral Dynamics</t>
+  </si>
+  <si>
+    <t>Dee Placeholder</t>
+  </si>
+  <si>
+    <t>SU-1</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Summer session I</t>
+  </si>
+  <si>
+    <t>14:45:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>13:00:00 - 15:30:00</t>
+  </si>
+  <si>
+    <t>Behavior in Sport</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:55:00</t>
+  </si>
+  <si>
+    <t>Stochastic Behavior</t>
+  </si>
+  <si>
+    <t>Eli Specimen, Dee Placeholder</t>
+  </si>
+  <si>
+    <t>DIGI</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:40:00</t>
+  </si>
+  <si>
+    <t>SB 110</t>
+  </si>
+  <si>
+    <t>Information Computing</t>
+  </si>
+  <si>
+    <t>Fay Mockson</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Network Optimization</t>
+  </si>
+  <si>
+    <t>Also listed as BHAV 306</t>
+  </si>
+  <si>
+    <t>BHAV 306</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>Adaptive Systems</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>Information Capstone</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>FA-1</t>
+  </si>
+  <si>
+    <t>Information Ethics</t>
+  </si>
+  <si>
+    <t>First half of the term</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>FA-2</t>
+  </si>
+  <si>
+    <t>Information Visualization</t>
+  </si>
+  <si>
+    <t>Second half of the term</t>
+  </si>
+  <si>
+    <t>SectionId</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>AcademicYear</t>
+  </si>
+  <si>
+    <t>MinimumCredits</t>
+  </si>
+  <si>
+    <t>MaximumCredits</t>
+  </si>
+  <si>
+    <t>StartTime</t>
+  </si>
+  <si>
+    <t>MeetingDuration</t>
+  </si>
+  <si>
+    <t>Classroom</t>
+  </si>
+  <si>
+    <t>CourseLevel</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>EnrollmentDay10</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS112-A</t>
+  </si>
+  <si>
+    <t>AY25</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS112-B</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS145-A</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS228-A</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS203-A</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS368-A</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV112-A</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV112-B</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV212-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV312-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI225-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI371-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI378-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI306-A</t>
+  </si>
+  <si>
+    <t>AY25-WI-AMUS181-A</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>AY25-WI-BHAV121-A</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS119-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS145-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS235-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS375-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV112-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV219-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI318-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI325-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-AMUS112-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-BHAV112-A</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Load</t>
+  </si>
+  <si>
+    <t>AY</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Choose</t>
+  </si>
+  <si>
+    <t>Bound</t>
+  </si>
+  <si>
+    <t>Gap</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Starts</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>DayRule</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>Meets</t>
+  </si>
+  <si>
+    <t>Intensive terms meet daily</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>WI, SU</t>
+  </si>
+  <si>
+    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
+  </si>
+  <si>
+    <t>allow</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>StartWeek</t>
+  </si>
+  <si>
+    <t>EndWeek</t>
+  </si>
+  <si>
+    <t>SpreadTerm</t>
+  </si>
+  <si>
+    <t>NonRoom</t>
+  </si>
+  <si>
+    <t>Off Campus</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Fall</t>
+  </si>
+  <si>
+    <t>Winter Intensive</t>
+  </si>
+  <si>
+    <t>Spring</t>
+  </si>
+  <si>
+    <t>Summer</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Full term</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>First half</t>
+  </si>
+  <si>
     <t>Second</t>
   </si>
   <si>
-    <t>SU-Second</t>
-  </si>
-  <si>
-    <t>Summer session II</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>11:00:00 - 12:05:00</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>Musical Patterns I (second semester)</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:20:00</t>
-  </si>
-  <si>
-    <t>NH 102</t>
-  </si>
-  <si>
-    <t>Musical Patterns II</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>WI-Full</t>
-  </si>
-  <si>
-    <t>Algorithms and Music</t>
-  </si>
-  <si>
-    <t>Cy Fictional</t>
-  </si>
-  <si>
-    <t>Winter intensive: meets every weekday for two weeks</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:05:00</t>
-  </si>
-  <si>
-    <t>NH 103</t>
-  </si>
-  <si>
-    <t>Discrete Rhythm</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>10:20:00 - 12:00:00</t>
-  </si>
-  <si>
-    <t>Harmonic Structures</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>Multivoice Analysis</t>
-  </si>
-  <si>
-    <t>368</t>
-  </si>
-  <si>
-    <t>14:10:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>NH 104</t>
-  </si>
-  <si>
-    <t>Corpus Studies I</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>Corpus Studies II</t>
-  </si>
-  <si>
-    <t>BHAV</t>
-  </si>
-  <si>
-    <t>13:30:00 - 14:35:00</t>
-  </si>
-  <si>
-    <t>NH 105</t>
-  </si>
-  <si>
-    <t>Introduction to Behavioral Dynamics</t>
-  </si>
-  <si>
-    <t>Dee Placeholder</t>
-  </si>
-  <si>
-    <t>First</t>
-  </si>
-  <si>
-    <t>SU-First</t>
-  </si>
-  <si>
-    <t>Online</t>
-  </si>
-  <si>
-    <t>Summer session I</t>
-  </si>
-  <si>
-    <t>14:45:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>13:00:00 - 15:30:00</t>
-  </si>
-  <si>
-    <t>Behavior in Sport</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>Behavioral Methods</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Models of Change</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:55:00</t>
-  </si>
-  <si>
-    <t>Stochastic Behavior</t>
-  </si>
-  <si>
-    <t>Eli Specimen, Dee Placeholder</t>
-  </si>
-  <si>
-    <t>DIGI</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:40:00</t>
-  </si>
-  <si>
-    <t>SB 110</t>
-  </si>
-  <si>
-    <t>Information Computing</t>
-  </si>
-  <si>
-    <t>Fay Mockson</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>Network Optimization</t>
-  </si>
-  <si>
-    <t>Also listed as BHAV 306</t>
-  </si>
-  <si>
-    <t>BHAV 306</t>
-  </si>
-  <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>Adaptive Systems</t>
-  </si>
-  <si>
-    <t>325</t>
-  </si>
-  <si>
-    <t>Information Capstone</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>FA-First</t>
-  </si>
-  <si>
-    <t>Information Ethics</t>
-  </si>
-  <si>
-    <t>First half of the term</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>FA-Second</t>
-  </si>
-  <si>
-    <t>Information Visualization</t>
-  </si>
-  <si>
-    <t>Second half of the term</t>
-  </si>
-  <si>
-    <t>SectionId</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>AcademicYear</t>
-  </si>
-  <si>
-    <t>MinimumCredits</t>
-  </si>
-  <si>
-    <t>MaximumCredits</t>
-  </si>
-  <si>
-    <t>StartTime</t>
-  </si>
-  <si>
-    <t>MeetingDuration</t>
-  </si>
-  <si>
-    <t>Classroom</t>
-  </si>
-  <si>
-    <t>CourseLevel</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Enrollment</t>
-  </si>
-  <si>
-    <t>EnrollmentDay10</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS112-A</t>
-  </si>
-  <si>
-    <t>AY25</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS112-B</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS145-A</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS228-A</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS203-A</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS368-A</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV112-A</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV112-B</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV212-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV312-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI225-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI371-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI378-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI306-A</t>
-  </si>
-  <si>
-    <t>AY25-WI-AMUS181-A</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>AY25-WI-BHAV121-A</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS119-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS145-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS235-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS375-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-BHAV112-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-BHAV219-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DIGI318-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DIGI325-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-AMUS112-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-BHAV112-A</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Load</t>
-  </si>
-  <si>
-    <t>AY</t>
-  </si>
-  <si>
-    <t>Constraint</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Course</t>
-  </si>
-  <si>
-    <t>Instructor</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Choose</t>
-  </si>
-  <si>
-    <t>Bound</t>
-  </si>
-  <si>
-    <t>Gap</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Starts</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>DayRule</t>
-  </si>
-  <si>
-    <t>From</t>
-  </si>
-  <si>
-    <t>To</t>
-  </si>
-  <si>
-    <t>Should</t>
-  </si>
-  <si>
-    <t>Meets</t>
-  </si>
-  <si>
-    <t>Intensive terms meet daily</t>
-  </si>
-  <si>
-    <t>standard</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>WI, SU</t>
-  </si>
-  <si>
-    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
-  </si>
-  <si>
-    <t>allow</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>StartWeek</t>
-  </si>
-  <si>
-    <t>EndWeek</t>
-  </si>
-  <si>
-    <t>SpreadTerm</t>
-  </si>
-  <si>
-    <t>NonRoom</t>
-  </si>
-  <si>
-    <t>Off Campus</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Fall</t>
-  </si>
-  <si>
-    <t>Winter Intensive</t>
-  </si>
-  <si>
-    <t>Spring</t>
-  </si>
-  <si>
-    <t>Summer</t>
-  </si>
-  <si>
-    <t>Part</t>
-  </si>
-  <si>
-    <t>Full term</t>
-  </si>
-  <si>
-    <t>First half</t>
-  </si>
-  <si>
     <t>Second half</t>
   </si>
   <si>
@@ -700,13 +712,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-04</t>
+    <t>2026-10-06</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>21:03:16</t>
+    <t>13:27:37</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -1114,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1133,9 +1145,11 @@
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="40" customWidth="1"/>
     <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1190,1741 +1204,2029 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" t="s">
+        <v>22</v>
+      </c>
+      <c r="T2" t="s">
+        <v>22</v>
+      </c>
+      <c r="U2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" t="s">
+        <v>22</v>
+      </c>
+      <c r="T3" t="s">
+        <v>22</v>
+      </c>
+      <c r="U3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>22</v>
+      </c>
+      <c r="R4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" t="s">
+        <v>22</v>
+      </c>
+      <c r="T4" t="s">
+        <v>22</v>
+      </c>
+      <c r="U4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
         <v>25</v>
       </c>
-      <c r="P2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="R2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>22</v>
+      </c>
+      <c r="R5" t="s">
+        <v>22</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+      <c r="T5" t="s">
+        <v>22</v>
+      </c>
+      <c r="U5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" t="s">
+        <v>37</v>
+      </c>
+      <c r="P6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R6" t="s">
+        <v>22</v>
+      </c>
+      <c r="S6" t="s">
+        <v>22</v>
+      </c>
+      <c r="T6" t="s">
+        <v>22</v>
+      </c>
+      <c r="U6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" t="s">
         <v>25</v>
       </c>
-      <c r="P3" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="K7" t="s">
         <v>26</v>
-      </c>
-      <c r="R3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>19</v>
-      </c>
-      <c r="R4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>19</v>
-      </c>
-      <c r="R5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" t="s">
-        <v>34</v>
-      </c>
-      <c r="P6" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>19</v>
-      </c>
-      <c r="R6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" t="s">
-        <v>23</v>
       </c>
       <c r="L7">
         <v>65</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>22</v>
+      </c>
+      <c r="R7" t="s">
+        <v>22</v>
+      </c>
+      <c r="S7" t="s">
+        <v>22</v>
+      </c>
+      <c r="T7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" t="s">
         <v>44</v>
       </c>
-      <c r="Q7" t="s">
-        <v>19</v>
-      </c>
-      <c r="R7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" t="s">
-        <v>41</v>
-      </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L8">
         <v>150</v>
       </c>
       <c r="M8" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8" t="s">
+        <v>33</v>
+      </c>
+      <c r="O8" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>54</v>
+      </c>
+      <c r="R8" t="s">
+        <v>22</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+      <c r="T8" t="s">
+        <v>22</v>
+      </c>
+      <c r="U8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" t="s">
         <v>42</v>
       </c>
-      <c r="N8" t="s">
-        <v>30</v>
-      </c>
-      <c r="O8" t="s">
-        <v>43</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="H9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" t="s">
         <v>44</v>
       </c>
-      <c r="Q8" t="s">
-        <v>51</v>
-      </c>
-      <c r="R8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
-      </c>
       <c r="J9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L9">
         <v>65</v>
       </c>
       <c r="M9" t="s">
+        <v>45</v>
+      </c>
+      <c r="N9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>22</v>
+      </c>
+      <c r="R9" t="s">
+        <v>22</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+      <c r="T9" t="s">
+        <v>22</v>
+      </c>
+      <c r="U9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" t="s">
         <v>42</v>
       </c>
-      <c r="N9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" t="s">
+      <c r="H10" t="s">
         <v>43</v>
       </c>
-      <c r="P9" t="s">
+      <c r="I10" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" t="s">
-        <v>19</v>
-      </c>
-      <c r="R9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" t="s">
-        <v>41</v>
-      </c>
       <c r="J10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L10">
         <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="N10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="O10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S10" t="s">
+        <v>22</v>
+      </c>
+      <c r="T10" t="s">
+        <v>22</v>
+      </c>
+      <c r="U10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L11">
         <v>65</v>
       </c>
       <c r="M11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" t="s">
+        <v>33</v>
+      </c>
+      <c r="O11" t="s">
+        <v>46</v>
+      </c>
+      <c r="P11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>22</v>
+      </c>
+      <c r="R11" t="s">
+        <v>22</v>
+      </c>
+      <c r="S11" t="s">
+        <v>22</v>
+      </c>
+      <c r="T11" t="s">
+        <v>22</v>
+      </c>
+      <c r="U11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
         <v>59</v>
       </c>
-      <c r="N11" t="s">
-        <v>30</v>
-      </c>
-      <c r="O11" t="s">
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" t="s">
         <v>43</v>
       </c>
-      <c r="P11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>19</v>
-      </c>
-      <c r="R11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" t="s">
-        <v>39</v>
-      </c>
-      <c r="H12" t="s">
-        <v>40</v>
-      </c>
       <c r="I12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L12">
         <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P12" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>22</v>
+      </c>
+      <c r="R12" t="s">
+        <v>22</v>
+      </c>
+      <c r="S12" t="s">
+        <v>22</v>
+      </c>
+      <c r="T12" t="s">
+        <v>22</v>
+      </c>
+      <c r="U12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" t="s">
         <v>44</v>
       </c>
-      <c r="Q12" t="s">
-        <v>19</v>
-      </c>
-      <c r="R12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" t="s">
-        <v>41</v>
-      </c>
       <c r="J13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L13">
         <v>150</v>
       </c>
       <c r="M13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q13" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S13" t="s">
+        <v>22</v>
+      </c>
+      <c r="T13" t="s">
+        <v>22</v>
+      </c>
+      <c r="U13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J14" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L14">
         <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="N14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S14" t="s">
+        <v>22</v>
+      </c>
+      <c r="T14" t="s">
+        <v>22</v>
+      </c>
+      <c r="U14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" t="s">
         <v>71</v>
       </c>
-      <c r="H15" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" t="s">
-        <v>68</v>
-      </c>
       <c r="J15" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S15" t="s">
+        <v>22</v>
+      </c>
+      <c r="T15" t="s">
+        <v>22</v>
+      </c>
+      <c r="U15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" t="s">
         <v>74</v>
       </c>
-      <c r="D16" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" t="s">
         <v>71</v>
       </c>
-      <c r="H16" t="s">
-        <v>72</v>
-      </c>
-      <c r="I16" t="s">
-        <v>68</v>
-      </c>
       <c r="J16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N16" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P16" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S16" t="s">
+        <v>22</v>
+      </c>
+      <c r="T16" t="s">
+        <v>22</v>
+      </c>
+      <c r="U16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J17" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N17" t="s">
+        <v>33</v>
+      </c>
+      <c r="O17" t="s">
+        <v>46</v>
+      </c>
+      <c r="P17" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>22</v>
+      </c>
+      <c r="R17" t="s">
+        <v>22</v>
+      </c>
+      <c r="S17" t="s">
+        <v>22</v>
+      </c>
+      <c r="T17" t="s">
+        <v>22</v>
+      </c>
+      <c r="U17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="O17" t="s">
-        <v>43</v>
-      </c>
-      <c r="P17" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>19</v>
-      </c>
-      <c r="R17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" t="s">
         <v>80</v>
       </c>
-      <c r="D18" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" t="s">
-        <v>38</v>
-      </c>
-      <c r="G18" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" t="s">
-        <v>77</v>
-      </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K18" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="N18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S18" t="s">
+        <v>22</v>
+      </c>
+      <c r="T18" t="s">
+        <v>22</v>
+      </c>
+      <c r="U18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L19">
         <v>65</v>
       </c>
       <c r="M19" t="s">
+        <v>88</v>
+      </c>
+      <c r="N19" t="s">
+        <v>89</v>
+      </c>
+      <c r="O19" t="s">
+        <v>46</v>
+      </c>
+      <c r="P19" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>22</v>
+      </c>
+      <c r="R19" t="s">
+        <v>22</v>
+      </c>
+      <c r="S19" t="s">
+        <v>22</v>
+      </c>
+      <c r="T19" t="s">
+        <v>22</v>
+      </c>
+      <c r="U19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" t="s">
         <v>85</v>
       </c>
-      <c r="N19" t="s">
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" t="s">
         <v>86</v>
       </c>
-      <c r="O19" t="s">
-        <v>43</v>
-      </c>
-      <c r="P19" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>19</v>
-      </c>
-      <c r="R19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20" t="s">
-        <v>83</v>
-      </c>
       <c r="I20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K20" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L20">
         <v>65</v>
       </c>
       <c r="M20" t="s">
+        <v>88</v>
+      </c>
+      <c r="N20" t="s">
+        <v>89</v>
+      </c>
+      <c r="O20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P20" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>22</v>
+      </c>
+      <c r="R20" t="s">
+        <v>22</v>
+      </c>
+      <c r="S20" t="s">
+        <v>22</v>
+      </c>
+      <c r="T20" t="s">
+        <v>22</v>
+      </c>
+      <c r="U20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" t="s">
         <v>85</v>
       </c>
-      <c r="N20" t="s">
-        <v>86</v>
-      </c>
-      <c r="O20" t="s">
-        <v>43</v>
-      </c>
-      <c r="P20" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>19</v>
-      </c>
-      <c r="R20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J21" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="K21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L21">
         <v>150</v>
       </c>
       <c r="M21" t="s">
+        <v>88</v>
+      </c>
+      <c r="N21" t="s">
+        <v>89</v>
+      </c>
+      <c r="O21" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>92</v>
+      </c>
+      <c r="R21" t="s">
+        <v>22</v>
+      </c>
+      <c r="S21" t="s">
+        <v>22</v>
+      </c>
+      <c r="T21" t="s">
+        <v>22</v>
+      </c>
+      <c r="U21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
         <v>85</v>
       </c>
-      <c r="N21" t="s">
-        <v>86</v>
-      </c>
-      <c r="O21" t="s">
-        <v>43</v>
-      </c>
-      <c r="P21" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>90</v>
-      </c>
-      <c r="R21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L22">
         <v>65</v>
       </c>
       <c r="M22" t="s">
+        <v>88</v>
+      </c>
+      <c r="N22" t="s">
+        <v>89</v>
+      </c>
+      <c r="O22" t="s">
+        <v>46</v>
+      </c>
+      <c r="P22" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>22</v>
+      </c>
+      <c r="R22" t="s">
+        <v>22</v>
+      </c>
+      <c r="S22" t="s">
+        <v>22</v>
+      </c>
+      <c r="T22" t="s">
+        <v>22</v>
+      </c>
+      <c r="U22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" t="s">
         <v>85</v>
       </c>
-      <c r="N22" t="s">
-        <v>86</v>
-      </c>
-      <c r="O22" t="s">
-        <v>43</v>
-      </c>
-      <c r="P22" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>19</v>
-      </c>
-      <c r="R22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" t="s">
-        <v>82</v>
-      </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J23" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L23">
         <v>150</v>
       </c>
       <c r="M23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O23" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S23" t="s">
+        <v>22</v>
+      </c>
+      <c r="T23" t="s">
+        <v>22</v>
+      </c>
+      <c r="U23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J24" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P24" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S24" t="s">
+        <v>22</v>
+      </c>
+      <c r="T24" t="s">
+        <v>22</v>
+      </c>
+      <c r="U24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G25" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H25" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K25" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O25" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P25" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S25" t="s">
+        <v>22</v>
+      </c>
+      <c r="T25" t="s">
+        <v>22</v>
+      </c>
+      <c r="U25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G26" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J26" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P26" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S26" t="s">
+        <v>22</v>
+      </c>
+      <c r="T26" t="s">
+        <v>22</v>
+      </c>
+      <c r="U26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J27" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N27" t="s">
+        <v>110</v>
+      </c>
+      <c r="O27" t="s">
+        <v>46</v>
+      </c>
+      <c r="P27" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>22</v>
+      </c>
+      <c r="R27" t="s">
+        <v>22</v>
+      </c>
+      <c r="S27" t="s">
+        <v>22</v>
+      </c>
+      <c r="T27" t="s">
+        <v>22</v>
+      </c>
+      <c r="U27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" t="s">
         <v>108</v>
       </c>
-      <c r="O27" t="s">
-        <v>43</v>
-      </c>
-      <c r="P27" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>19</v>
-      </c>
-      <c r="R27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" t="s">
-        <v>38</v>
-      </c>
-      <c r="G28" t="s">
-        <v>39</v>
-      </c>
-      <c r="H28" t="s">
-        <v>53</v>
-      </c>
-      <c r="I28" t="s">
-        <v>106</v>
-      </c>
       <c r="J28" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K28" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L28">
         <v>65</v>
       </c>
       <c r="M28" t="s">
+        <v>112</v>
+      </c>
+      <c r="N28" t="s">
         <v>110</v>
       </c>
-      <c r="N28" t="s">
+      <c r="O28" t="s">
+        <v>46</v>
+      </c>
+      <c r="P28" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>113</v>
+      </c>
+      <c r="R28" t="s">
+        <v>114</v>
+      </c>
+      <c r="S28" t="s">
+        <v>22</v>
+      </c>
+      <c r="T28" t="s">
+        <v>22</v>
+      </c>
+      <c r="U28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" t="s">
         <v>108</v>
       </c>
-      <c r="O28" t="s">
-        <v>43</v>
-      </c>
-      <c r="P28" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>111</v>
-      </c>
-      <c r="R28" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" t="s">
-        <v>38</v>
-      </c>
-      <c r="G29" t="s">
-        <v>39</v>
-      </c>
-      <c r="H29" t="s">
-        <v>53</v>
-      </c>
-      <c r="I29" t="s">
-        <v>106</v>
-      </c>
       <c r="J29" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K29" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L29">
         <v>65</v>
       </c>
       <c r="M29" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N29" t="s">
+        <v>110</v>
+      </c>
+      <c r="O29" t="s">
+        <v>46</v>
+      </c>
+      <c r="P29" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>22</v>
+      </c>
+      <c r="R29" t="s">
+        <v>22</v>
+      </c>
+      <c r="S29" t="s">
+        <v>22</v>
+      </c>
+      <c r="T29" t="s">
+        <v>22</v>
+      </c>
+      <c r="U29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30" t="s">
+        <v>102</v>
+      </c>
+      <c r="I30" t="s">
         <v>108</v>
       </c>
-      <c r="O29" t="s">
-        <v>43</v>
-      </c>
-      <c r="P29" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>19</v>
-      </c>
-      <c r="R29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" t="s">
-        <v>115</v>
-      </c>
-      <c r="D30" t="s">
-        <v>37</v>
-      </c>
-      <c r="E30" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" t="s">
-        <v>38</v>
-      </c>
-      <c r="G30" t="s">
-        <v>71</v>
-      </c>
-      <c r="H30" t="s">
-        <v>100</v>
-      </c>
-      <c r="I30" t="s">
-        <v>106</v>
-      </c>
       <c r="J30" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K30" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N30" t="s">
+        <v>110</v>
+      </c>
+      <c r="O30" t="s">
+        <v>46</v>
+      </c>
+      <c r="P30" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>22</v>
+      </c>
+      <c r="R30" t="s">
+        <v>22</v>
+      </c>
+      <c r="S30" t="s">
+        <v>22</v>
+      </c>
+      <c r="T30" t="s">
+        <v>22</v>
+      </c>
+      <c r="U30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31" t="s">
+        <v>74</v>
+      </c>
+      <c r="H31" t="s">
+        <v>80</v>
+      </c>
+      <c r="I31" t="s">
         <v>108</v>
       </c>
-      <c r="O30" t="s">
-        <v>43</v>
-      </c>
-      <c r="P30" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>19</v>
-      </c>
-      <c r="R30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" t="s">
-        <v>103</v>
-      </c>
-      <c r="C31" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
-      </c>
-      <c r="G31" t="s">
-        <v>71</v>
-      </c>
-      <c r="H31" t="s">
-        <v>77</v>
-      </c>
-      <c r="I31" t="s">
-        <v>106</v>
-      </c>
       <c r="J31" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="K31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N31" t="s">
+        <v>110</v>
+      </c>
+      <c r="O31" t="s">
+        <v>46</v>
+      </c>
+      <c r="P31" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>122</v>
+      </c>
+      <c r="R31" t="s">
+        <v>22</v>
+      </c>
+      <c r="S31" t="s">
+        <v>22</v>
+      </c>
+      <c r="T31" t="s">
+        <v>22</v>
+      </c>
+      <c r="U31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32" t="s">
+        <v>50</v>
+      </c>
+      <c r="G32" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" t="s">
+        <v>80</v>
+      </c>
+      <c r="I32" t="s">
         <v>108</v>
       </c>
-      <c r="O31" t="s">
-        <v>43</v>
-      </c>
-      <c r="P31" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>120</v>
-      </c>
-      <c r="R31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" t="s">
-        <v>46</v>
-      </c>
-      <c r="G32" t="s">
-        <v>71</v>
-      </c>
-      <c r="H32" t="s">
-        <v>77</v>
-      </c>
-      <c r="I32" t="s">
-        <v>106</v>
-      </c>
       <c r="J32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O32" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P32" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="R32" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="S32" t="s">
+        <v>22</v>
+      </c>
+      <c r="T32" t="s">
+        <v>22</v>
+      </c>
+      <c r="U32" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2935,7 +3237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -2960,17 +3262,18 @@
     <col min="22" max="22" width="40" customWidth="1"/>
     <col min="23" max="23" width="12" customWidth="1"/>
     <col min="24" max="24" width="17" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -2994,22 +3297,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -3018,10 +3321,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -3030,39 +3333,45 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -3071,72 +3380,78 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O2">
         <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
         <v>140</v>
       </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>138</v>
-      </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -3145,72 +3460,78 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O3">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -3219,72 +3540,78 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O4">
         <v>65</v>
       </c>
       <c r="P4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="R4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -3293,72 +3620,78 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="R5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3367,72 +3700,78 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3441,72 +3780,78 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="R7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3515,72 +3860,78 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O8">
         <v>65</v>
       </c>
       <c r="P8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R8" t="s">
+        <v>46</v>
+      </c>
+      <c r="S8" t="s">
+        <v>22</v>
+      </c>
+      <c r="T8" t="s">
+        <v>22</v>
+      </c>
+      <c r="U8" t="s">
+        <v>47</v>
+      </c>
+      <c r="V8" t="s">
+        <v>22</v>
+      </c>
+      <c r="W8" t="s">
+        <v>22</v>
+      </c>
+      <c r="X8" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
         <v>85</v>
       </c>
-      <c r="R8" t="s">
-        <v>43</v>
-      </c>
-      <c r="S8" t="s">
-        <v>19</v>
-      </c>
-      <c r="T8" t="s">
-        <v>19</v>
-      </c>
-      <c r="U8" t="s">
-        <v>44</v>
-      </c>
-      <c r="V8" t="s">
-        <v>19</v>
-      </c>
-      <c r="W8" t="s">
-        <v>19</v>
-      </c>
-      <c r="X8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>82</v>
-      </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -3589,72 +3940,78 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O9">
         <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q9" t="s">
+        <v>88</v>
+      </c>
+      <c r="R9" t="s">
+        <v>46</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+      <c r="T9" t="s">
+        <v>22</v>
+      </c>
+      <c r="U9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V9" t="s">
+        <v>22</v>
+      </c>
+      <c r="W9" t="s">
+        <v>22</v>
+      </c>
+      <c r="X9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
         <v>85</v>
       </c>
-      <c r="R9" t="s">
-        <v>43</v>
-      </c>
-      <c r="S9" t="s">
-        <v>19</v>
-      </c>
-      <c r="T9" t="s">
-        <v>19</v>
-      </c>
-      <c r="U9" t="s">
-        <v>44</v>
-      </c>
-      <c r="V9" t="s">
-        <v>19</v>
-      </c>
-      <c r="W9" t="s">
-        <v>19</v>
-      </c>
-      <c r="X9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" t="s">
-        <v>82</v>
-      </c>
       <c r="G10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -3663,72 +4020,78 @@
         <v>4</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -3737,72 +4100,78 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H12" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -3811,72 +4180,78 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="R12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -3885,72 +4260,78 @@
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="R13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="W13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -3959,72 +4340,78 @@
         <v>2</v>
       </c>
       <c r="L14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="W14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4033,72 +4420,78 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M15" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O15">
         <v>65</v>
       </c>
       <c r="P15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="R15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="W15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I16" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -4107,72 +4500,78 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O16">
         <v>150</v>
       </c>
       <c r="P16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q16" t="s">
+        <v>66</v>
+      </c>
+      <c r="R16" t="s">
+        <v>46</v>
+      </c>
+      <c r="S16" t="s">
+        <v>22</v>
+      </c>
+      <c r="T16" t="s">
+        <v>22</v>
+      </c>
+      <c r="U16" t="s">
+        <v>47</v>
+      </c>
+      <c r="V16" t="s">
+        <v>68</v>
+      </c>
+      <c r="W16" t="s">
+        <v>22</v>
+      </c>
+      <c r="X16" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" t="s">
         <v>63</v>
       </c>
-      <c r="R16" t="s">
-        <v>43</v>
-      </c>
-      <c r="S16" t="s">
-        <v>19</v>
-      </c>
-      <c r="T16" t="s">
-        <v>19</v>
-      </c>
-      <c r="U16" t="s">
-        <v>44</v>
-      </c>
-      <c r="V16" t="s">
-        <v>65</v>
-      </c>
-      <c r="W16" t="s">
-        <v>19</v>
-      </c>
-      <c r="X16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>162</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" t="s">
-        <v>138</v>
-      </c>
-      <c r="D17" t="s">
-        <v>60</v>
-      </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -4181,72 +4580,78 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M17" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O17">
         <v>150</v>
       </c>
       <c r="P17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="R17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U17" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" t="s">
         <v>27</v>
-      </c>
-      <c r="E18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I18" t="s">
-        <v>24</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -4255,72 +4660,78 @@
         <v>4</v>
       </c>
       <c r="L18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O18">
         <v>65</v>
       </c>
       <c r="P18" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q18" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H19" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -4329,72 +4740,78 @@
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M19" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N19" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O19">
         <v>65</v>
       </c>
       <c r="P19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="R19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I20" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -4403,72 +4820,78 @@
         <v>4</v>
       </c>
       <c r="L20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q20" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="R20" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U20" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -4477,72 +4900,78 @@
         <v>4</v>
       </c>
       <c r="L21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M21" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q21" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U21" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H22" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I22" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -4551,72 +4980,78 @@
         <v>4</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M22" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N22" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O22">
         <v>65</v>
       </c>
       <c r="P22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q22" t="s">
+        <v>88</v>
+      </c>
+      <c r="R22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S22" t="s">
+        <v>22</v>
+      </c>
+      <c r="T22" t="s">
+        <v>22</v>
+      </c>
+      <c r="U22" t="s">
+        <v>47</v>
+      </c>
+      <c r="V22" t="s">
+        <v>22</v>
+      </c>
+      <c r="W22" t="s">
+        <v>22</v>
+      </c>
+      <c r="X22" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>171</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
         <v>85</v>
       </c>
-      <c r="R22" t="s">
-        <v>43</v>
-      </c>
-      <c r="S22" t="s">
-        <v>19</v>
-      </c>
-      <c r="T22" t="s">
-        <v>19</v>
-      </c>
-      <c r="U22" t="s">
-        <v>44</v>
-      </c>
-      <c r="V22" t="s">
-        <v>19</v>
-      </c>
-      <c r="W22" t="s">
-        <v>19</v>
-      </c>
-      <c r="X22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>169</v>
-      </c>
-      <c r="B23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C23" t="s">
-        <v>138</v>
-      </c>
-      <c r="D23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" t="s">
-        <v>82</v>
-      </c>
       <c r="G23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -4625,72 +5060,78 @@
         <v>4</v>
       </c>
       <c r="L23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N23" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q23" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R23" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W23" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -4699,72 +5140,78 @@
         <v>4</v>
       </c>
       <c r="L24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N24" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O24">
         <v>65</v>
       </c>
       <c r="P24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U24" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E25" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F25" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G25" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H25" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I25" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J25">
         <v>4</v>
@@ -4773,72 +5220,78 @@
         <v>4</v>
       </c>
       <c r="L25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M25" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N25" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="R25" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U25" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W25" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G26" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H26" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I26" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -4847,72 +5300,78 @@
         <v>2</v>
       </c>
       <c r="L26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M26" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N26" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O26">
         <v>150</v>
       </c>
       <c r="P26" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q26" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R26" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U26" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="V26" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="W26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H27" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I27" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -4921,43 +5380,49 @@
         <v>2</v>
       </c>
       <c r="L27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M27" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N27" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O27">
         <v>150</v>
       </c>
       <c r="P27" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q27" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="R27" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="V27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="W27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X27" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -4978,7 +5443,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4989,13 +5454,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -5017,19 +5482,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -5037,62 +5502,62 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
         <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -5127,61 +5592,61 @@
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>16</v>
@@ -5189,188 +5654,188 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="M2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="N2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
+        <v>200</v>
+      </c>
+      <c r="K3" t="s">
+        <v>201</v>
+      </c>
+      <c r="L3" t="s">
+        <v>163</v>
+      </c>
+      <c r="M3" t="s">
         <v>198</v>
       </c>
-      <c r="K3" t="s">
-        <v>199</v>
-      </c>
-      <c r="L3" t="s">
-        <v>161</v>
-      </c>
-      <c r="M3" t="s">
-        <v>196</v>
-      </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J4" t="s">
+        <v>200</v>
+      </c>
+      <c r="K4" t="s">
+        <v>201</v>
+      </c>
+      <c r="L4" t="s">
+        <v>165</v>
+      </c>
+      <c r="M4" t="s">
         <v>198</v>
       </c>
-      <c r="K4" t="s">
-        <v>199</v>
-      </c>
-      <c r="L4" t="s">
-        <v>163</v>
-      </c>
-      <c r="M4" t="s">
-        <v>196</v>
-      </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="T4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -5392,122 +5857,122 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5515,19 +5980,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5535,19 +6000,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5555,19 +6020,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5575,33 +6040,33 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5612,16 +6077,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="C12" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5632,16 +6097,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>219</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -5652,16 +6117,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5672,16 +6137,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -5692,16 +6157,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B16" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C16" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -5712,16 +6177,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B17" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E17">
         <v>13</v>
@@ -5732,16 +6197,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5767,90 +6232,90 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B7" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B8" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web/public/examples/example-schedule.xlsx
+++ b/apps/web/public/examples/example-schedule.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="247">
   <si>
     <t>Term</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Level</t>
   </si>
   <si>
+    <t>Colocations</t>
+  </si>
+  <si>
     <t>FA</t>
   </si>
   <si>
@@ -604,6 +607,15 @@
     <t>Meets</t>
   </si>
   <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
     <t>Intensive terms meet daily</t>
   </si>
   <si>
@@ -616,6 +628,9 @@
     <t>WI, SU</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
   </si>
   <si>
@@ -712,13 +727,13 @@
     <t>Export Date</t>
   </si>
   <si>
-    <t>2026-10-06</t>
+    <t>2026-10-07</t>
   </si>
   <si>
     <t>Export Time</t>
   </si>
   <si>
-    <t>13:27:37</t>
+    <t>08:51:36</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -734,9 +749,6 @@
   </si>
   <si>
     <t>Time Stamp In File Name</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
   <si>
     <t>Default Department</t>
@@ -1126,7 +1138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1147,9 +1159,10 @@
     <col min="18" max="18" width="15" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="7" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1213,2020 +1226,2116 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" t="s">
+        <v>35</v>
+      </c>
+      <c r="P4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S4" t="s">
+        <v>23</v>
+      </c>
+      <c r="T4" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>23</v>
+      </c>
+      <c r="R5" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" t="s">
+        <v>23</v>
+      </c>
+      <c r="T5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" t="s">
+        <v>23</v>
+      </c>
+      <c r="V5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" t="s">
+        <v>23</v>
+      </c>
+      <c r="T6" t="s">
+        <v>23</v>
+      </c>
+      <c r="U6" t="s">
+        <v>23</v>
+      </c>
+      <c r="V6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="K7" t="s">
         <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" t="s">
-        <v>22</v>
-      </c>
-      <c r="T2" t="s">
-        <v>22</v>
-      </c>
-      <c r="U2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" t="s">
-        <v>22</v>
-      </c>
-      <c r="T3" t="s">
-        <v>22</v>
-      </c>
-      <c r="U3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P4" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>22</v>
-      </c>
-      <c r="R4" t="s">
-        <v>22</v>
-      </c>
-      <c r="S4" t="s">
-        <v>22</v>
-      </c>
-      <c r="T4" t="s">
-        <v>22</v>
-      </c>
-      <c r="U4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" t="s">
-        <v>37</v>
-      </c>
-      <c r="P5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>22</v>
-      </c>
-      <c r="R5" t="s">
-        <v>22</v>
-      </c>
-      <c r="S5" t="s">
-        <v>22</v>
-      </c>
-      <c r="T5" t="s">
-        <v>22</v>
-      </c>
-      <c r="U5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" t="s">
-        <v>36</v>
-      </c>
-      <c r="O6" t="s">
-        <v>37</v>
-      </c>
-      <c r="P6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R6" t="s">
-        <v>22</v>
-      </c>
-      <c r="S6" t="s">
-        <v>22</v>
-      </c>
-      <c r="T6" t="s">
-        <v>22</v>
-      </c>
-      <c r="U6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" t="s">
-        <v>44</v>
-      </c>
-      <c r="J7" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" t="s">
-        <v>26</v>
       </c>
       <c r="L7">
         <v>65</v>
       </c>
       <c r="M7" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R7" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7" t="s">
+        <v>23</v>
+      </c>
+      <c r="U7" t="s">
+        <v>49</v>
+      </c>
+      <c r="V7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" t="s">
         <v>45</v>
       </c>
-      <c r="N7" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" t="s">
-        <v>46</v>
-      </c>
-      <c r="P7" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>22</v>
-      </c>
-      <c r="R7" t="s">
-        <v>22</v>
-      </c>
-      <c r="S7" t="s">
-        <v>22</v>
-      </c>
-      <c r="T7" t="s">
-        <v>22</v>
-      </c>
-      <c r="U7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="J8" t="s">
         <v>51</v>
       </c>
-      <c r="H8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" t="s">
-        <v>44</v>
-      </c>
-      <c r="J8" t="s">
-        <v>50</v>
-      </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L8">
         <v>150</v>
       </c>
       <c r="M8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" t="s">
+        <v>47</v>
+      </c>
+      <c r="P8" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>55</v>
+      </c>
+      <c r="R8" t="s">
+        <v>23</v>
+      </c>
+      <c r="S8" t="s">
+        <v>23</v>
+      </c>
+      <c r="T8" t="s">
+        <v>23</v>
+      </c>
+      <c r="U8" t="s">
+        <v>49</v>
+      </c>
+      <c r="V8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I9" t="s">
         <v>45</v>
       </c>
-      <c r="N8" t="s">
-        <v>33</v>
-      </c>
-      <c r="O8" t="s">
-        <v>46</v>
-      </c>
-      <c r="P8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>54</v>
-      </c>
-      <c r="R8" t="s">
-        <v>22</v>
-      </c>
-      <c r="S8" t="s">
-        <v>22</v>
-      </c>
-      <c r="T8" t="s">
-        <v>22</v>
-      </c>
-      <c r="U8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" t="s">
-        <v>44</v>
-      </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L9">
         <v>65</v>
       </c>
       <c r="M9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" t="s">
+        <v>47</v>
+      </c>
+      <c r="P9" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>23</v>
+      </c>
+      <c r="R9" t="s">
+        <v>23</v>
+      </c>
+      <c r="S9" t="s">
+        <v>23</v>
+      </c>
+      <c r="T9" t="s">
+        <v>23</v>
+      </c>
+      <c r="U9" t="s">
+        <v>49</v>
+      </c>
+      <c r="V9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" t="s">
         <v>45</v>
       </c>
-      <c r="N9" t="s">
-        <v>27</v>
-      </c>
-      <c r="O9" t="s">
-        <v>46</v>
-      </c>
-      <c r="P9" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>22</v>
-      </c>
-      <c r="R9" t="s">
-        <v>22</v>
-      </c>
-      <c r="S9" t="s">
-        <v>22</v>
-      </c>
-      <c r="T9" t="s">
-        <v>22</v>
-      </c>
-      <c r="U9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" t="s">
-        <v>44</v>
-      </c>
       <c r="J10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L10">
         <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S10" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" t="s">
+        <v>23</v>
+      </c>
+      <c r="U10" t="s">
+        <v>49</v>
+      </c>
+      <c r="V10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" t="s">
         <v>27</v>
-      </c>
-      <c r="O10" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>22</v>
-      </c>
-      <c r="R10" t="s">
-        <v>22</v>
-      </c>
-      <c r="S10" t="s">
-        <v>22</v>
-      </c>
-      <c r="T10" t="s">
-        <v>22</v>
-      </c>
-      <c r="U10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" t="s">
-        <v>61</v>
-      </c>
-      <c r="J11" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" t="s">
-        <v>26</v>
       </c>
       <c r="L11">
         <v>65</v>
       </c>
       <c r="M11" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O11" t="s">
+        <v>47</v>
+      </c>
+      <c r="P11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>23</v>
+      </c>
+      <c r="R11" t="s">
+        <v>23</v>
+      </c>
+      <c r="S11" t="s">
+        <v>23</v>
+      </c>
+      <c r="T11" t="s">
+        <v>23</v>
+      </c>
+      <c r="U11" t="s">
+        <v>49</v>
+      </c>
+      <c r="V11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" t="s">
         <v>62</v>
       </c>
-      <c r="N11" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" t="s">
-        <v>46</v>
-      </c>
-      <c r="P11" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>22</v>
-      </c>
-      <c r="R11" t="s">
-        <v>22</v>
-      </c>
-      <c r="S11" t="s">
-        <v>22</v>
-      </c>
-      <c r="T11" t="s">
-        <v>22</v>
-      </c>
-      <c r="U11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" t="s">
-        <v>61</v>
-      </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L12">
         <v>65</v>
       </c>
       <c r="M12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="V12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L13">
         <v>150</v>
       </c>
       <c r="M13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R13" t="s">
+        <v>23</v>
+      </c>
+      <c r="S13" t="s">
+        <v>23</v>
+      </c>
+      <c r="T13" t="s">
+        <v>23</v>
+      </c>
+      <c r="U13" t="s">
+        <v>49</v>
+      </c>
+      <c r="V13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="S13" t="s">
-        <v>22</v>
-      </c>
-      <c r="T13" t="s">
-        <v>22</v>
-      </c>
-      <c r="U13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L14">
         <v>65</v>
       </c>
       <c r="M14" t="s">
+        <v>73</v>
+      </c>
+      <c r="N14" t="s">
+        <v>68</v>
+      </c>
+      <c r="O14" t="s">
+        <v>47</v>
+      </c>
+      <c r="P14" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>23</v>
+      </c>
+      <c r="R14" t="s">
+        <v>23</v>
+      </c>
+      <c r="S14" t="s">
+        <v>23</v>
+      </c>
+      <c r="T14" t="s">
+        <v>23</v>
+      </c>
+      <c r="U14" t="s">
+        <v>49</v>
+      </c>
+      <c r="V14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" t="s">
         <v>72</v>
       </c>
-      <c r="N14" t="s">
-        <v>67</v>
-      </c>
-      <c r="O14" t="s">
-        <v>46</v>
-      </c>
-      <c r="P14" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>22</v>
-      </c>
-      <c r="R14" t="s">
-        <v>22</v>
-      </c>
-      <c r="S14" t="s">
-        <v>22</v>
-      </c>
-      <c r="T14" t="s">
-        <v>22</v>
-      </c>
-      <c r="U14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" t="s">
-        <v>75</v>
-      </c>
-      <c r="I15" t="s">
-        <v>71</v>
-      </c>
       <c r="J15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15" t="s">
+        <v>77</v>
+      </c>
+      <c r="N15" t="s">
+        <v>68</v>
+      </c>
+      <c r="O15" t="s">
+        <v>47</v>
+      </c>
+      <c r="P15" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>23</v>
+      </c>
+      <c r="R15" t="s">
+        <v>23</v>
+      </c>
+      <c r="S15" t="s">
+        <v>23</v>
+      </c>
+      <c r="T15" t="s">
+        <v>23</v>
+      </c>
+      <c r="U15" t="s">
+        <v>49</v>
+      </c>
+      <c r="V15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" t="s">
         <v>76</v>
       </c>
-      <c r="N15" t="s">
-        <v>67</v>
-      </c>
-      <c r="O15" t="s">
-        <v>46</v>
-      </c>
-      <c r="P15" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>22</v>
-      </c>
-      <c r="R15" t="s">
-        <v>22</v>
-      </c>
-      <c r="S15" t="s">
-        <v>22</v>
-      </c>
-      <c r="T15" t="s">
-        <v>22</v>
-      </c>
-      <c r="U15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" t="s">
-        <v>75</v>
-      </c>
       <c r="I16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q16" t="s">
+        <v>23</v>
+      </c>
+      <c r="R16" t="s">
+        <v>23</v>
+      </c>
+      <c r="S16" t="s">
+        <v>23</v>
+      </c>
+      <c r="T16" t="s">
+        <v>23</v>
+      </c>
+      <c r="U16" t="s">
+        <v>49</v>
+      </c>
+      <c r="V16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>22</v>
       </c>
-      <c r="R16" t="s">
-        <v>22</v>
-      </c>
-      <c r="S16" t="s">
-        <v>22</v>
-      </c>
-      <c r="T16" t="s">
-        <v>22</v>
-      </c>
-      <c r="U16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17" t="s">
+        <v>83</v>
+      </c>
+      <c r="N17" t="s">
+        <v>34</v>
+      </c>
+      <c r="O17" t="s">
+        <v>47</v>
+      </c>
+      <c r="P17" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>23</v>
+      </c>
+      <c r="R17" t="s">
+        <v>23</v>
+      </c>
+      <c r="S17" t="s">
+        <v>23</v>
+      </c>
+      <c r="T17" t="s">
+        <v>23</v>
+      </c>
+      <c r="U17" t="s">
+        <v>49</v>
+      </c>
+      <c r="V17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s">
+        <v>81</v>
+      </c>
+      <c r="I18" t="s">
         <v>82</v>
       </c>
-      <c r="N17" t="s">
-        <v>33</v>
-      </c>
-      <c r="O17" t="s">
-        <v>46</v>
-      </c>
-      <c r="P17" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>22</v>
-      </c>
-      <c r="R17" t="s">
-        <v>22</v>
-      </c>
-      <c r="S17" t="s">
-        <v>22</v>
-      </c>
-      <c r="T17" t="s">
-        <v>22</v>
-      </c>
-      <c r="U17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" t="s">
-        <v>80</v>
-      </c>
-      <c r="I18" t="s">
-        <v>81</v>
-      </c>
       <c r="J18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q18" t="s">
+        <v>23</v>
+      </c>
+      <c r="R18" t="s">
+        <v>23</v>
+      </c>
+      <c r="S18" t="s">
+        <v>23</v>
+      </c>
+      <c r="T18" t="s">
+        <v>23</v>
+      </c>
+      <c r="U18" t="s">
+        <v>49</v>
+      </c>
+      <c r="V18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>22</v>
       </c>
-      <c r="R18" t="s">
-        <v>22</v>
-      </c>
-      <c r="S18" t="s">
-        <v>22</v>
-      </c>
-      <c r="T18" t="s">
-        <v>22</v>
-      </c>
-      <c r="U18" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L19">
         <v>65</v>
       </c>
       <c r="M19" t="s">
+        <v>89</v>
+      </c>
+      <c r="N19" t="s">
+        <v>90</v>
+      </c>
+      <c r="O19" t="s">
+        <v>47</v>
+      </c>
+      <c r="P19" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>23</v>
+      </c>
+      <c r="R19" t="s">
+        <v>23</v>
+      </c>
+      <c r="S19" t="s">
+        <v>23</v>
+      </c>
+      <c r="T19" t="s">
+        <v>23</v>
+      </c>
+      <c r="U19" t="s">
+        <v>49</v>
+      </c>
+      <c r="V19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" t="s">
         <v>88</v>
       </c>
-      <c r="N19" t="s">
-        <v>89</v>
-      </c>
-      <c r="O19" t="s">
-        <v>46</v>
-      </c>
-      <c r="P19" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>22</v>
-      </c>
-      <c r="R19" t="s">
-        <v>22</v>
-      </c>
-      <c r="S19" t="s">
-        <v>22</v>
-      </c>
-      <c r="T19" t="s">
-        <v>22</v>
-      </c>
-      <c r="U19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" t="s">
-        <v>86</v>
-      </c>
-      <c r="I20" t="s">
-        <v>87</v>
-      </c>
       <c r="J20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L20">
         <v>65</v>
       </c>
       <c r="M20" t="s">
+        <v>89</v>
+      </c>
+      <c r="N20" t="s">
+        <v>90</v>
+      </c>
+      <c r="O20" t="s">
+        <v>47</v>
+      </c>
+      <c r="P20" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>23</v>
+      </c>
+      <c r="R20" t="s">
+        <v>23</v>
+      </c>
+      <c r="S20" t="s">
+        <v>23</v>
+      </c>
+      <c r="T20" t="s">
+        <v>23</v>
+      </c>
+      <c r="U20" t="s">
+        <v>49</v>
+      </c>
+      <c r="V20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21" t="s">
         <v>88</v>
       </c>
-      <c r="N20" t="s">
-        <v>89</v>
-      </c>
-      <c r="O20" t="s">
-        <v>46</v>
-      </c>
-      <c r="P20" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>22</v>
-      </c>
-      <c r="R20" t="s">
-        <v>22</v>
-      </c>
-      <c r="S20" t="s">
-        <v>22</v>
-      </c>
-      <c r="T20" t="s">
-        <v>22</v>
-      </c>
-      <c r="U20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G21" t="s">
-        <v>51</v>
-      </c>
-      <c r="H21" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" t="s">
-        <v>87</v>
-      </c>
       <c r="J21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L21">
         <v>150</v>
       </c>
       <c r="M21" t="s">
+        <v>89</v>
+      </c>
+      <c r="N21" t="s">
+        <v>90</v>
+      </c>
+      <c r="O21" t="s">
+        <v>47</v>
+      </c>
+      <c r="P21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>93</v>
+      </c>
+      <c r="R21" t="s">
+        <v>23</v>
+      </c>
+      <c r="S21" t="s">
+        <v>23</v>
+      </c>
+      <c r="T21" t="s">
+        <v>23</v>
+      </c>
+      <c r="U21" t="s">
+        <v>49</v>
+      </c>
+      <c r="V21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22" t="s">
         <v>88</v>
       </c>
-      <c r="N21" t="s">
-        <v>89</v>
-      </c>
-      <c r="O21" t="s">
-        <v>46</v>
-      </c>
-      <c r="P21" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>92</v>
-      </c>
-      <c r="R21" t="s">
-        <v>22</v>
-      </c>
-      <c r="S21" t="s">
-        <v>22</v>
-      </c>
-      <c r="T21" t="s">
-        <v>22</v>
-      </c>
-      <c r="U21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" t="s">
-        <v>55</v>
-      </c>
-      <c r="E22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" t="s">
-        <v>93</v>
-      </c>
-      <c r="I22" t="s">
-        <v>87</v>
-      </c>
       <c r="J22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L22">
         <v>65</v>
       </c>
       <c r="M22" t="s">
+        <v>89</v>
+      </c>
+      <c r="N22" t="s">
+        <v>90</v>
+      </c>
+      <c r="O22" t="s">
+        <v>47</v>
+      </c>
+      <c r="P22" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>23</v>
+      </c>
+      <c r="R22" t="s">
+        <v>23</v>
+      </c>
+      <c r="S22" t="s">
+        <v>23</v>
+      </c>
+      <c r="T22" t="s">
+        <v>23</v>
+      </c>
+      <c r="U22" t="s">
+        <v>49</v>
+      </c>
+      <c r="V22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" t="s">
         <v>88</v>
       </c>
-      <c r="N22" t="s">
-        <v>89</v>
-      </c>
-      <c r="O22" t="s">
-        <v>46</v>
-      </c>
-      <c r="P22" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>22</v>
-      </c>
-      <c r="R22" t="s">
-        <v>22</v>
-      </c>
-      <c r="S22" t="s">
-        <v>22</v>
-      </c>
-      <c r="T22" t="s">
-        <v>22</v>
-      </c>
-      <c r="U22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" t="s">
-        <v>41</v>
-      </c>
-      <c r="G23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H23" t="s">
-        <v>95</v>
-      </c>
-      <c r="I23" t="s">
-        <v>87</v>
-      </c>
       <c r="J23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L23">
         <v>150</v>
       </c>
       <c r="M23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q23" t="s">
+        <v>23</v>
+      </c>
+      <c r="R23" t="s">
+        <v>23</v>
+      </c>
+      <c r="S23" t="s">
+        <v>23</v>
+      </c>
+      <c r="T23" t="s">
+        <v>23</v>
+      </c>
+      <c r="U23" t="s">
+        <v>49</v>
+      </c>
+      <c r="V23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="R23" t="s">
-        <v>22</v>
-      </c>
-      <c r="S23" t="s">
-        <v>22</v>
-      </c>
-      <c r="T23" t="s">
-        <v>22</v>
-      </c>
-      <c r="U23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="V24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N25" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q25" t="s">
+        <v>23</v>
+      </c>
+      <c r="R25" t="s">
+        <v>23</v>
+      </c>
+      <c r="S25" t="s">
+        <v>23</v>
+      </c>
+      <c r="T25" t="s">
+        <v>23</v>
+      </c>
+      <c r="U25" t="s">
+        <v>49</v>
+      </c>
+      <c r="V25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>22</v>
       </c>
-      <c r="R25" t="s">
-        <v>22</v>
-      </c>
-      <c r="S25" t="s">
-        <v>22</v>
-      </c>
-      <c r="T25" t="s">
-        <v>22</v>
-      </c>
-      <c r="U25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q26" t="s">
+        <v>23</v>
+      </c>
+      <c r="R26" t="s">
+        <v>23</v>
+      </c>
+      <c r="S26" t="s">
+        <v>23</v>
+      </c>
+      <c r="T26" t="s">
+        <v>23</v>
+      </c>
+      <c r="U26" t="s">
+        <v>49</v>
+      </c>
+      <c r="V26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>22</v>
       </c>
-      <c r="R26" t="s">
-        <v>22</v>
-      </c>
-      <c r="S26" t="s">
-        <v>22</v>
-      </c>
-      <c r="T26" t="s">
-        <v>22</v>
-      </c>
-      <c r="U26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>21</v>
-      </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27" t="s">
+        <v>110</v>
+      </c>
+      <c r="N27" t="s">
+        <v>111</v>
+      </c>
+      <c r="O27" t="s">
+        <v>47</v>
+      </c>
+      <c r="P27" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>23</v>
+      </c>
+      <c r="R27" t="s">
+        <v>23</v>
+      </c>
+      <c r="S27" t="s">
+        <v>23</v>
+      </c>
+      <c r="T27" t="s">
+        <v>23</v>
+      </c>
+      <c r="U27" t="s">
+        <v>49</v>
+      </c>
+      <c r="V27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" t="s">
+        <v>57</v>
+      </c>
+      <c r="I28" t="s">
         <v>109</v>
       </c>
-      <c r="N27" t="s">
-        <v>110</v>
-      </c>
-      <c r="O27" t="s">
-        <v>46</v>
-      </c>
-      <c r="P27" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>22</v>
-      </c>
-      <c r="R27" t="s">
-        <v>22</v>
-      </c>
-      <c r="S27" t="s">
-        <v>22</v>
-      </c>
-      <c r="T27" t="s">
-        <v>22</v>
-      </c>
-      <c r="U27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" t="s">
-        <v>42</v>
-      </c>
-      <c r="H28" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" t="s">
-        <v>108</v>
-      </c>
       <c r="J28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L28">
         <v>65</v>
       </c>
       <c r="M28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="S28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="V28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L29">
         <v>65</v>
       </c>
       <c r="M29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="V29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q30" t="s">
+        <v>23</v>
+      </c>
+      <c r="R30" t="s">
+        <v>23</v>
+      </c>
+      <c r="S30" t="s">
+        <v>23</v>
+      </c>
+      <c r="T30" t="s">
+        <v>23</v>
+      </c>
+      <c r="U30" t="s">
+        <v>49</v>
+      </c>
+      <c r="V30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>22</v>
       </c>
-      <c r="R30" t="s">
-        <v>22</v>
-      </c>
-      <c r="S30" t="s">
-        <v>22</v>
-      </c>
-      <c r="T30" t="s">
-        <v>22</v>
-      </c>
-      <c r="U30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>21</v>
-      </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R31" t="s">
+        <v>23</v>
+      </c>
+      <c r="S31" t="s">
+        <v>23</v>
+      </c>
+      <c r="T31" t="s">
+        <v>23</v>
+      </c>
+      <c r="U31" t="s">
+        <v>49</v>
+      </c>
+      <c r="V31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>22</v>
       </c>
-      <c r="S31" t="s">
-        <v>22</v>
-      </c>
-      <c r="T31" t="s">
-        <v>22</v>
-      </c>
-      <c r="U31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>21</v>
-      </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U32" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="V32" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3267,13 +3376,13 @@
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -3297,22 +3406,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -3321,10 +3430,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -3333,10 +3442,10 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>18</v>
@@ -3347,31 +3456,31 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2">
         <v>4</v>
@@ -3380,78 +3489,78 @@
         <v>4</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O2">
         <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -3460,78 +3569,78 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O3">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -3540,78 +3649,78 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O4">
         <v>65</v>
       </c>
       <c r="P4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -3620,78 +3729,78 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3700,78 +3809,78 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -3780,78 +3889,78 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3860,78 +3969,78 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O8">
         <v>65</v>
       </c>
       <c r="P8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -3940,78 +4049,78 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O9">
         <v>65</v>
       </c>
       <c r="P9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -4020,78 +4129,78 @@
         <v>4</v>
       </c>
       <c r="L10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>140</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -4100,78 +4209,78 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" t="s">
-        <v>140</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -4180,78 +4289,78 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="R12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" t="s">
         <v>22</v>
       </c>
-      <c r="C13" t="s">
-        <v>140</v>
-      </c>
-      <c r="D13" t="s">
-        <v>21</v>
-      </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -4260,78 +4369,78 @@
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="W13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" t="s">
         <v>22</v>
       </c>
-      <c r="C14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -4340,78 +4449,78 @@
         <v>2</v>
       </c>
       <c r="L14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="W14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" t="s">
         <v>22</v>
       </c>
-      <c r="C15" t="s">
-        <v>140</v>
-      </c>
-      <c r="D15" t="s">
-        <v>21</v>
-      </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G15" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" t="s">
         <v>111</v>
-      </c>
-      <c r="H15" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" t="s">
-        <v>110</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4420,78 +4529,78 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O15">
         <v>65</v>
       </c>
       <c r="P15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="W15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -4500,78 +4609,78 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O16">
         <v>150</v>
       </c>
       <c r="P16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="W16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -4580,78 +4689,78 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O17">
         <v>150</v>
       </c>
       <c r="P17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -4660,78 +4769,78 @@
         <v>4</v>
       </c>
       <c r="L18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O18">
         <v>65</v>
       </c>
       <c r="P18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -4740,78 +4849,78 @@
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O19">
         <v>65</v>
       </c>
       <c r="P19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -4820,78 +4929,78 @@
         <v>4</v>
       </c>
       <c r="L20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -4900,78 +5009,78 @@
         <v>4</v>
       </c>
       <c r="L21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -4980,78 +5089,78 @@
         <v>4</v>
       </c>
       <c r="L22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O22">
         <v>65</v>
       </c>
       <c r="P22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -5060,78 +5169,78 @@
         <v>4</v>
       </c>
       <c r="L23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -5140,78 +5249,78 @@
         <v>4</v>
       </c>
       <c r="L24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O24">
         <v>65</v>
       </c>
       <c r="P24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J25">
         <v>4</v>
@@ -5220,78 +5329,78 @@
         <v>4</v>
       </c>
       <c r="L25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I26" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J26">
         <v>2</v>
@@ -5300,78 +5409,78 @@
         <v>2</v>
       </c>
       <c r="L26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N26" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O26">
         <v>150</v>
       </c>
       <c r="P26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -5380,49 +5489,49 @@
         <v>2</v>
       </c>
       <c r="L27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O27">
         <v>150</v>
       </c>
       <c r="P27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -5443,7 +5552,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5454,13 +5563,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -5482,19 +5591,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -5502,62 +5611,62 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -5568,7 +5677,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -5587,255 +5696,293 @@
     <col min="17" max="17" width="4" customWidth="1"/>
     <col min="18" max="18" width="8" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="40" customWidth="1"/>
+    <col min="21" max="21" width="10" customWidth="1"/>
+    <col min="22" max="22" width="8" customWidth="1"/>
+    <col min="23" max="23" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" t="s">
+        <v>203</v>
+      </c>
+      <c r="W2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>195</v>
-      </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K3" t="s">
+        <v>206</v>
+      </c>
+      <c r="L3" t="s">
+        <v>164</v>
+      </c>
+      <c r="M3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" t="s">
+        <v>203</v>
+      </c>
+      <c r="W3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" t="s">
         <v>200</v>
       </c>
-      <c r="K3" t="s">
-        <v>201</v>
-      </c>
-      <c r="L3" t="s">
-        <v>163</v>
-      </c>
-      <c r="M3" t="s">
-        <v>198</v>
-      </c>
-      <c r="N3" t="s">
-        <v>51</v>
-      </c>
-      <c r="O3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>22</v>
-      </c>
-      <c r="R3" t="s">
-        <v>22</v>
-      </c>
-      <c r="S3" t="s">
-        <v>22</v>
-      </c>
-      <c r="T3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4" t="s">
-        <v>196</v>
-      </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="L4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T4" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="U4" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" t="s">
+        <v>203</v>
+      </c>
+      <c r="W4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -5857,122 +6004,122 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B6" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5980,19 +6127,19 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -6000,19 +6147,19 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6020,19 +6167,19 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6040,33 +6187,33 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -6077,16 +6224,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B12" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C12" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -6097,16 +6244,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B13" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13">
         <v>9</v>
@@ -6117,16 +6264,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -6137,16 +6284,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -6157,16 +6304,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B16" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C16" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16">
         <v>9</v>
@@ -6177,16 +6324,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B17" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C17" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17">
         <v>13</v>
@@ -6197,16 +6344,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6232,90 +6379,90 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B7" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B8" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web/public/examples/example-schedule.xlsx
+++ b/apps/web/public/examples/example-schedule.xlsx
@@ -211,465 +211,465 @@
     <t>Musical Patterns II</t>
   </si>
   <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>SP-0</t>
+  </si>
+  <si>
+    <t>Algorithms and Music</t>
+  </si>
+  <si>
+    <t>Cy Fictional</t>
+  </si>
+  <si>
+    <t>Winter intensive: meets every weekday for two weeks</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:05:00</t>
+  </si>
+  <si>
+    <t>NH 103</t>
+  </si>
+  <si>
+    <t>Discrete Rhythm</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>10:20:00 - 12:00:00</t>
+  </si>
+  <si>
+    <t>Harmonic Structures</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>Multivoice Analysis</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>14:10:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>NH 104</t>
+  </si>
+  <si>
+    <t>Corpus Studies I</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Corpus Studies II</t>
+  </si>
+  <si>
+    <t>BHAV</t>
+  </si>
+  <si>
+    <t>13:30:00 - 14:35:00</t>
+  </si>
+  <si>
+    <t>NH 105</t>
+  </si>
+  <si>
+    <t>Introduction to Behavioral Dynamics</t>
+  </si>
+  <si>
+    <t>Dee Placeholder</t>
+  </si>
+  <si>
+    <t>SU-1</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Summer session I</t>
+  </si>
+  <si>
+    <t>14:45:00 - 15:50:00</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>13:00:00 - 15:30:00</t>
+  </si>
+  <si>
+    <t>Behavior in Sport</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Behavioral Methods</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Models of Change</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>12:15:00 - 13:55:00</t>
+  </si>
+  <si>
+    <t>Stochastic Behavior</t>
+  </si>
+  <si>
+    <t>Eli Specimen, Dee Placeholder</t>
+  </si>
+  <si>
+    <t>DIGI</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>08:00:00 - 09:40:00</t>
+  </si>
+  <si>
+    <t>SB 110</t>
+  </si>
+  <si>
+    <t>Information Computing</t>
+  </si>
+  <si>
+    <t>Fay Mockson</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Network Optimization</t>
+  </si>
+  <si>
+    <t>Also listed as BHAV 306</t>
+  </si>
+  <si>
+    <t>BHAV 306</t>
+  </si>
+  <si>
+    <t>318</t>
+  </si>
+  <si>
+    <t>Adaptive Systems</t>
+  </si>
+  <si>
+    <t>325</t>
+  </si>
+  <si>
+    <t>Information Capstone</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>FA-1</t>
+  </si>
+  <si>
+    <t>Information Ethics</t>
+  </si>
+  <si>
+    <t>First half of the term</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>FA-2</t>
+  </si>
+  <si>
+    <t>Information Visualization</t>
+  </si>
+  <si>
+    <t>Second half of the term</t>
+  </si>
+  <si>
+    <t>SectionId</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>AcademicYear</t>
+  </si>
+  <si>
+    <t>MinimumCredits</t>
+  </si>
+  <si>
+    <t>MaximumCredits</t>
+  </si>
+  <si>
+    <t>StartTime</t>
+  </si>
+  <si>
+    <t>MeetingDuration</t>
+  </si>
+  <si>
+    <t>Classroom</t>
+  </si>
+  <si>
+    <t>CourseLevel</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Enrollment</t>
+  </si>
+  <si>
+    <t>EnrollmentDay10</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS112-A</t>
+  </si>
+  <si>
+    <t>AY25</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS112-B</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS145-A</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS228-A</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS203-A</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>AY25-FA-AMUS368-A</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV112-A</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV112-B</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV212-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-BHAV312-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI225-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI371-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI378-A</t>
+  </si>
+  <si>
+    <t>AY25-FA-DIGI306-A</t>
+  </si>
+  <si>
+    <t>AY25-WI-AMUS181-A</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>AY25-WI-BHAV121-A</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS119-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS145-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS235-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-AMUS375-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV112-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-BHAV219-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI318-A</t>
+  </si>
+  <si>
+    <t>AY25-SP-DIGI325-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-AMUS112-A</t>
+  </si>
+  <si>
+    <t>AY25-SU-BHAV112-A</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Load</t>
+  </si>
+  <si>
+    <t>AY</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Choose</t>
+  </si>
+  <si>
+    <t>Bound</t>
+  </si>
+  <si>
+    <t>Gap</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Starts</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>DayRule</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>Meets</t>
+  </si>
+  <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Intensive terms meet daily</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>WI, SU</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
+  </si>
+  <si>
+    <t>allow</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>StartWeek</t>
+  </si>
+  <si>
+    <t>EndWeek</t>
+  </si>
+  <si>
+    <t>SpreadTerm</t>
+  </si>
+  <si>
+    <t>NonRoom</t>
+  </si>
+  <si>
+    <t>Off Campus</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Fall</t>
+  </si>
+  <si>
     <t>WI</t>
   </si>
   <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>WI-Full</t>
-  </si>
-  <si>
-    <t>Algorithms and Music</t>
-  </si>
-  <si>
-    <t>Cy Fictional</t>
-  </si>
-  <si>
-    <t>Winter intensive: meets every weekday for two weeks</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:05:00</t>
-  </si>
-  <si>
-    <t>NH 103</t>
-  </si>
-  <si>
-    <t>Discrete Rhythm</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>10:20:00 - 12:00:00</t>
-  </si>
-  <si>
-    <t>Harmonic Structures</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>Multivoice Analysis</t>
-  </si>
-  <si>
-    <t>368</t>
-  </si>
-  <si>
-    <t>14:10:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>NH 104</t>
-  </si>
-  <si>
-    <t>Corpus Studies I</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>Corpus Studies II</t>
-  </si>
-  <si>
-    <t>BHAV</t>
-  </si>
-  <si>
-    <t>13:30:00 - 14:35:00</t>
-  </si>
-  <si>
-    <t>NH 105</t>
-  </si>
-  <si>
-    <t>Introduction to Behavioral Dynamics</t>
-  </si>
-  <si>
-    <t>Dee Placeholder</t>
-  </si>
-  <si>
-    <t>SU-1</t>
-  </si>
-  <si>
-    <t>Online</t>
-  </si>
-  <si>
-    <t>Summer session I</t>
-  </si>
-  <si>
-    <t>14:45:00 - 15:50:00</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>13:00:00 - 15:30:00</t>
-  </si>
-  <si>
-    <t>Behavior in Sport</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>Behavioral Methods</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>Models of Change</t>
-  </si>
-  <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>12:15:00 - 13:55:00</t>
-  </si>
-  <si>
-    <t>Stochastic Behavior</t>
-  </si>
-  <si>
-    <t>Eli Specimen, Dee Placeholder</t>
-  </si>
-  <si>
-    <t>DIGI</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t>08:00:00 - 09:40:00</t>
-  </si>
-  <si>
-    <t>SB 110</t>
-  </si>
-  <si>
-    <t>Information Computing</t>
-  </si>
-  <si>
-    <t>Fay Mockson</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>Network Optimization</t>
-  </si>
-  <si>
-    <t>Also listed as BHAV 306</t>
-  </si>
-  <si>
-    <t>BHAV 306</t>
-  </si>
-  <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>Adaptive Systems</t>
-  </si>
-  <si>
-    <t>325</t>
-  </si>
-  <si>
-    <t>Information Capstone</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>FA-1</t>
-  </si>
-  <si>
-    <t>Information Ethics</t>
-  </si>
-  <si>
-    <t>First half of the term</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>FA-2</t>
-  </si>
-  <si>
-    <t>Information Visualization</t>
-  </si>
-  <si>
-    <t>Second half of the term</t>
-  </si>
-  <si>
-    <t>SectionId</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>AcademicYear</t>
-  </si>
-  <si>
-    <t>MinimumCredits</t>
-  </si>
-  <si>
-    <t>MaximumCredits</t>
-  </si>
-  <si>
-    <t>StartTime</t>
-  </si>
-  <si>
-    <t>MeetingDuration</t>
-  </si>
-  <si>
-    <t>Classroom</t>
-  </si>
-  <si>
-    <t>CourseLevel</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Enrollment</t>
-  </si>
-  <si>
-    <t>EnrollmentDay10</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS112-A</t>
-  </si>
-  <si>
-    <t>AY25</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS112-B</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS145-A</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS228-A</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS203-A</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>AY25-FA-AMUS368-A</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV112-A</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV112-B</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV212-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-BHAV312-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI225-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI371-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI378-A</t>
-  </si>
-  <si>
-    <t>AY25-FA-DIGI306-A</t>
-  </si>
-  <si>
-    <t>AY25-WI-AMUS181-A</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>AY25-WI-BHAV121-A</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS119-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS145-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS235-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-AMUS375-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-BHAV112-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-BHAV219-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DIGI318-A</t>
-  </si>
-  <si>
-    <t>AY25-SP-DIGI325-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-AMUS112-A</t>
-  </si>
-  <si>
-    <t>AY25-SU-BHAV112-A</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Load</t>
-  </si>
-  <si>
-    <t>AY</t>
-  </si>
-  <si>
-    <t>Constraint</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Course</t>
-  </si>
-  <si>
-    <t>Instructor</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Choose</t>
-  </si>
-  <si>
-    <t>Bound</t>
-  </si>
-  <si>
-    <t>Gap</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Starts</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>DayRule</t>
-  </si>
-  <si>
-    <t>From</t>
-  </si>
-  <si>
-    <t>To</t>
-  </si>
-  <si>
-    <t>Should</t>
-  </si>
-  <si>
-    <t>Meets</t>
-  </si>
-  <si>
-    <t>Element</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Intensive terms meet daily</t>
-  </si>
-  <si>
-    <t>standard</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>WI, SU</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Winter and summer courses meet every weekday for a few hours; these times are not in the university's list.</t>
-  </si>
-  <si>
-    <t>allow</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>StartWeek</t>
-  </si>
-  <si>
-    <t>EndWeek</t>
-  </si>
-  <si>
-    <t>SpreadTerm</t>
-  </si>
-  <si>
-    <t>NonRoom</t>
-  </si>
-  <si>
-    <t>Off Campus</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>Fall</t>
-  </si>
-  <si>
     <t>Winter Intensive</t>
   </si>
   <si>
@@ -733,7 +733,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>08:51:36</t>
+    <t>12:17:42</t>
   </si>
   <si>
     <t>Academic Year</t>
@@ -1980,13 +1980,13 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
         <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
         <v>41</v>
@@ -2007,19 +2007,19 @@
         <v>45</v>
       </c>
       <c r="J13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L13">
         <v>150</v>
       </c>
       <c r="M13" t="s">
+        <v>66</v>
+      </c>
+      <c r="N13" t="s">
         <v>67</v>
-      </c>
-      <c r="N13" t="s">
-        <v>68</v>
       </c>
       <c r="O13" t="s">
         <v>47</v>
@@ -2028,7 +2028,7 @@
         <v>48</v>
       </c>
       <c r="Q13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R13" t="s">
         <v>23</v>
@@ -2054,7 +2054,7 @@
         <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
@@ -2069,10 +2069,10 @@
         <v>43</v>
       </c>
       <c r="H14" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" t="s">
         <v>71</v>
-      </c>
-      <c r="I14" t="s">
-        <v>72</v>
       </c>
       <c r="J14" t="s">
         <v>26</v>
@@ -2084,10 +2084,10 @@
         <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O14" t="s">
         <v>47</v>
@@ -2122,7 +2122,7 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>41</v>
@@ -2134,13 +2134,13 @@
         <v>42</v>
       </c>
       <c r="G15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" t="s">
         <v>75</v>
       </c>
-      <c r="H15" t="s">
-        <v>76</v>
-      </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J15" t="s">
         <v>26</v>
@@ -2152,10 +2152,10 @@
         <v>100</v>
       </c>
       <c r="M15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O15" t="s">
         <v>47</v>
@@ -2190,7 +2190,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
         <v>41</v>
@@ -2202,13 +2202,13 @@
         <v>42</v>
       </c>
       <c r="G16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" t="s">
         <v>75</v>
       </c>
-      <c r="H16" t="s">
-        <v>76</v>
-      </c>
       <c r="I16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J16" t="s">
         <v>26</v>
@@ -2220,10 +2220,10 @@
         <v>100</v>
       </c>
       <c r="M16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O16" t="s">
         <v>47</v>
@@ -2258,7 +2258,7 @@
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
         <v>41</v>
@@ -2270,13 +2270,13 @@
         <v>42</v>
       </c>
       <c r="G17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" t="s">
         <v>81</v>
-      </c>
-      <c r="I17" t="s">
-        <v>82</v>
       </c>
       <c r="J17" t="s">
         <v>26</v>
@@ -2288,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="M17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N17" t="s">
         <v>34</v>
@@ -2326,7 +2326,7 @@
         <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
         <v>41</v>
@@ -2338,13 +2338,13 @@
         <v>42</v>
       </c>
       <c r="G18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H18" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" t="s">
         <v>81</v>
-      </c>
-      <c r="I18" t="s">
-        <v>82</v>
       </c>
       <c r="J18" t="s">
         <v>26</v>
@@ -2356,7 +2356,7 @@
         <v>100</v>
       </c>
       <c r="M18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N18" t="s">
         <v>34</v>
@@ -2391,7 +2391,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
         <v>40</v>
@@ -2409,10 +2409,10 @@
         <v>43</v>
       </c>
       <c r="H19" t="s">
+        <v>86</v>
+      </c>
+      <c r="I19" t="s">
         <v>87</v>
-      </c>
-      <c r="I19" t="s">
-        <v>88</v>
       </c>
       <c r="J19" t="s">
         <v>26</v>
@@ -2424,10 +2424,10 @@
         <v>65</v>
       </c>
       <c r="M19" t="s">
+        <v>88</v>
+      </c>
+      <c r="N19" t="s">
         <v>89</v>
-      </c>
-      <c r="N19" t="s">
-        <v>90</v>
       </c>
       <c r="O19" t="s">
         <v>47</v>
@@ -2459,7 +2459,7 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
         <v>40</v>
@@ -2477,10 +2477,10 @@
         <v>43</v>
       </c>
       <c r="H20" t="s">
+        <v>86</v>
+      </c>
+      <c r="I20" t="s">
         <v>87</v>
-      </c>
-      <c r="I20" t="s">
-        <v>88</v>
       </c>
       <c r="J20" t="s">
         <v>26</v>
@@ -2492,10 +2492,10 @@
         <v>65</v>
       </c>
       <c r="M20" t="s">
+        <v>88</v>
+      </c>
+      <c r="N20" t="s">
         <v>89</v>
-      </c>
-      <c r="N20" t="s">
-        <v>90</v>
       </c>
       <c r="O20" t="s">
         <v>47</v>
@@ -2527,7 +2527,7 @@
         <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
         <v>40</v>
@@ -2548,31 +2548,31 @@
         <v>53</v>
       </c>
       <c r="I21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J21" t="s">
         <v>33</v>
       </c>
       <c r="K21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L21">
         <v>150</v>
       </c>
       <c r="M21" t="s">
+        <v>88</v>
+      </c>
+      <c r="N21" t="s">
         <v>89</v>
-      </c>
-      <c r="N21" t="s">
-        <v>90</v>
       </c>
       <c r="O21" t="s">
         <v>47</v>
       </c>
       <c r="P21" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q21" t="s">
         <v>92</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>93</v>
       </c>
       <c r="R21" t="s">
         <v>23</v>
@@ -2595,7 +2595,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
         <v>40</v>
@@ -2613,10 +2613,10 @@
         <v>43</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J22" t="s">
         <v>26</v>
@@ -2628,10 +2628,10 @@
         <v>65</v>
       </c>
       <c r="M22" t="s">
+        <v>88</v>
+      </c>
+      <c r="N22" t="s">
         <v>89</v>
-      </c>
-      <c r="N22" t="s">
-        <v>90</v>
       </c>
       <c r="O22" t="s">
         <v>47</v>
@@ -2660,13 +2660,13 @@
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
         <v>41</v>
@@ -2681,22 +2681,22 @@
         <v>52</v>
       </c>
       <c r="H23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L23">
         <v>150</v>
       </c>
       <c r="M23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N23" t="s">
         <v>37</v>
@@ -2731,10 +2731,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
         <v>41</v>
@@ -2746,13 +2746,13 @@
         <v>42</v>
       </c>
       <c r="G24" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24" t="s">
         <v>75</v>
       </c>
-      <c r="H24" t="s">
-        <v>76</v>
-      </c>
       <c r="I24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J24" t="s">
         <v>26</v>
@@ -2764,7 +2764,7 @@
         <v>100</v>
       </c>
       <c r="M24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N24" t="s">
         <v>37</v>
@@ -2799,10 +2799,10 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
         <v>41</v>
@@ -2814,13 +2814,13 @@
         <v>42</v>
       </c>
       <c r="G25" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25" t="s">
         <v>75</v>
       </c>
-      <c r="H25" t="s">
-        <v>76</v>
-      </c>
       <c r="I25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s">
         <v>26</v>
@@ -2832,7 +2832,7 @@
         <v>100</v>
       </c>
       <c r="M25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N25" t="s">
         <v>37</v>
@@ -2867,10 +2867,10 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
         <v>41</v>
@@ -2882,13 +2882,13 @@
         <v>42</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J26" t="s">
         <v>26</v>
@@ -2900,10 +2900,10 @@
         <v>100</v>
       </c>
       <c r="M26" t="s">
+        <v>103</v>
+      </c>
+      <c r="N26" t="s">
         <v>104</v>
-      </c>
-      <c r="N26" t="s">
-        <v>105</v>
       </c>
       <c r="O26" t="s">
         <v>47</v>
@@ -2935,10 +2935,10 @@
         <v>22</v>
       </c>
       <c r="B27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" t="s">
         <v>106</v>
-      </c>
-      <c r="C27" t="s">
-        <v>107</v>
       </c>
       <c r="D27" t="s">
         <v>41</v>
@@ -2950,13 +2950,13 @@
         <v>42</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H27" t="s">
+        <v>107</v>
+      </c>
+      <c r="I27" t="s">
         <v>108</v>
-      </c>
-      <c r="I27" t="s">
-        <v>109</v>
       </c>
       <c r="J27" t="s">
         <v>26</v>
@@ -2968,10 +2968,10 @@
         <v>100</v>
       </c>
       <c r="M27" t="s">
+        <v>109</v>
+      </c>
+      <c r="N27" t="s">
         <v>110</v>
-      </c>
-      <c r="N27" t="s">
-        <v>111</v>
       </c>
       <c r="O27" t="s">
         <v>47</v>
@@ -3003,10 +3003,10 @@
         <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
         <v>41</v>
@@ -3024,7 +3024,7 @@
         <v>57</v>
       </c>
       <c r="I28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J28" t="s">
         <v>26</v>
@@ -3036,10 +3036,10 @@
         <v>65</v>
       </c>
       <c r="M28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O28" t="s">
         <v>47</v>
@@ -3048,10 +3048,10 @@
         <v>48</v>
       </c>
       <c r="Q28" t="s">
+        <v>113</v>
+      </c>
+      <c r="R28" t="s">
         <v>114</v>
-      </c>
-      <c r="R28" t="s">
-        <v>115</v>
       </c>
       <c r="S28" t="s">
         <v>23</v>
@@ -3071,10 +3071,10 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
         <v>41</v>
@@ -3092,7 +3092,7 @@
         <v>57</v>
       </c>
       <c r="I29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J29" t="s">
         <v>26</v>
@@ -3104,10 +3104,10 @@
         <v>65</v>
       </c>
       <c r="M29" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O29" t="s">
         <v>47</v>
@@ -3139,10 +3139,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
         <v>41</v>
@@ -3154,13 +3154,13 @@
         <v>42</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J30" t="s">
         <v>26</v>
@@ -3172,10 +3172,10 @@
         <v>100</v>
       </c>
       <c r="M30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O30" t="s">
         <v>47</v>
@@ -3207,10 +3207,10 @@
         <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>41</v>
@@ -3222,28 +3222,28 @@
         <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J31" t="s">
         <v>33</v>
       </c>
       <c r="K31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N31" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O31" t="s">
         <v>47</v>
@@ -3252,7 +3252,7 @@
         <v>48</v>
       </c>
       <c r="Q31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R31" t="s">
         <v>23</v>
@@ -3275,10 +3275,10 @@
         <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
         <v>41</v>
@@ -3290,28 +3290,28 @@
         <v>51</v>
       </c>
       <c r="G32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J32" t="s">
         <v>51</v>
       </c>
       <c r="K32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O32" t="s">
         <v>47</v>
@@ -3320,7 +3320,7 @@
         <v>48</v>
       </c>
       <c r="Q32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R32" t="s">
         <v>23</v>
@@ -3376,13 +3376,13 @@
   <sheetData>
     <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -3406,22 +3406,22 @@
         <v>5</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
@@ -3430,10 +3430,10 @@
         <v>14</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>15</v>
@@ -3442,10 +3442,10 @@
         <v>16</v>
       </c>
       <c r="W1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>18</v>
@@ -3456,13 +3456,13 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>140</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>141</v>
       </c>
       <c r="D2" t="s">
         <v>22</v>
@@ -3495,7 +3495,7 @@
         <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O2">
         <v>65</v>
@@ -3536,13 +3536,13 @@
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -3575,7 +3575,7 @@
         <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O3">
         <v>65</v>
@@ -3616,13 +3616,13 @@
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -3655,7 +3655,7 @@
         <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O4">
         <v>65</v>
@@ -3696,13 +3696,13 @@
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -3714,13 +3714,13 @@
         <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H5" t="s">
         <v>41</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -3732,19 +3732,19 @@
         <v>23</v>
       </c>
       <c r="M5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R5" t="s">
         <v>47</v>
@@ -3776,13 +3776,13 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -3794,13 +3794,13 @@
         <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H6" t="s">
         <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -3815,16 +3815,16 @@
         <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O6">
         <v>65</v>
       </c>
       <c r="P6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q6" t="s">
         <v>72</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>73</v>
       </c>
       <c r="R6" t="s">
         <v>47</v>
@@ -3856,13 +3856,13 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -3874,7 +3874,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s">
         <v>41</v>
@@ -3892,19 +3892,19 @@
         <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q7" t="s">
         <v>82</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>83</v>
       </c>
       <c r="R7" t="s">
         <v>47</v>
@@ -3936,13 +3936,13 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -3951,7 +3951,7 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G8" t="s">
         <v>40</v>
@@ -3960,7 +3960,7 @@
         <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -3975,16 +3975,16 @@
         <v>43</v>
       </c>
       <c r="N8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O8">
         <v>65</v>
       </c>
       <c r="P8" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q8" t="s">
         <v>88</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>89</v>
       </c>
       <c r="R8" t="s">
         <v>47</v>
@@ -4016,13 +4016,13 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B9" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -4031,7 +4031,7 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G9" t="s">
         <v>40</v>
@@ -4040,7 +4040,7 @@
         <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -4055,16 +4055,16 @@
         <v>43</v>
       </c>
       <c r="N9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O9">
         <v>65</v>
       </c>
       <c r="P9" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q9" t="s">
         <v>88</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>89</v>
       </c>
       <c r="R9" t="s">
         <v>47</v>
@@ -4096,13 +4096,13 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -4111,10 +4111,10 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H10" t="s">
         <v>41</v>
@@ -4132,19 +4132,19 @@
         <v>23</v>
       </c>
       <c r="M10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R10" t="s">
         <v>47</v>
@@ -4176,13 +4176,13 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B11" t="s">
         <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
@@ -4191,16 +4191,16 @@
         <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H11" t="s">
         <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -4212,19 +4212,19 @@
         <v>23</v>
       </c>
       <c r="M11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R11" t="s">
         <v>47</v>
@@ -4256,13 +4256,13 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
@@ -4271,16 +4271,16 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" t="s">
         <v>106</v>
-      </c>
-      <c r="G12" t="s">
-        <v>107</v>
       </c>
       <c r="H12" t="s">
         <v>41</v>
       </c>
       <c r="I12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -4292,19 +4292,19 @@
         <v>23</v>
       </c>
       <c r="M12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q12" t="s">
         <v>109</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>110</v>
       </c>
       <c r="R12" t="s">
         <v>47</v>
@@ -4336,13 +4336,13 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
@@ -4351,16 +4351,16 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H13" t="s">
         <v>41</v>
       </c>
       <c r="I13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -4372,19 +4372,19 @@
         <v>23</v>
       </c>
       <c r="M13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R13" t="s">
         <v>47</v>
@@ -4399,7 +4399,7 @@
         <v>48</v>
       </c>
       <c r="V13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W13" t="s">
         <v>23</v>
@@ -4416,13 +4416,13 @@
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s">
         <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
@@ -4431,16 +4431,16 @@
         <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H14" t="s">
         <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -4452,19 +4452,19 @@
         <v>23</v>
       </c>
       <c r="M14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R14" t="s">
         <v>47</v>
@@ -4479,7 +4479,7 @@
         <v>48</v>
       </c>
       <c r="V14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="W14" t="s">
         <v>23</v>
@@ -4496,13 +4496,13 @@
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s">
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
@@ -4511,16 +4511,16 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H15" t="s">
         <v>41</v>
       </c>
       <c r="I15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J15">
         <v>4</v>
@@ -4535,16 +4535,16 @@
         <v>43</v>
       </c>
       <c r="N15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O15">
         <v>65</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="R15" t="s">
         <v>47</v>
@@ -4559,7 +4559,7 @@
         <v>48</v>
       </c>
       <c r="V15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="W15" t="s">
         <v>23</v>
@@ -4576,31 +4576,31 @@
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
         <v>39</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H16" t="s">
         <v>41</v>
       </c>
       <c r="I16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -4615,7 +4615,7 @@
         <v>52</v>
       </c>
       <c r="N16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O16">
         <v>150</v>
@@ -4624,7 +4624,7 @@
         <v>45</v>
       </c>
       <c r="Q16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R16" t="s">
         <v>47</v>
@@ -4639,7 +4639,7 @@
         <v>48</v>
       </c>
       <c r="V16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="W16" t="s">
         <v>23</v>
@@ -4656,25 +4656,25 @@
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H17" t="s">
         <v>41</v>
@@ -4695,16 +4695,16 @@
         <v>52</v>
       </c>
       <c r="N17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O17">
         <v>150</v>
       </c>
       <c r="P17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R17" t="s">
         <v>47</v>
@@ -4736,13 +4736,13 @@
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D18" t="s">
         <v>31</v>
@@ -4775,7 +4775,7 @@
         <v>43</v>
       </c>
       <c r="N18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O18">
         <v>65</v>
@@ -4816,13 +4816,13 @@
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D19" t="s">
         <v>31</v>
@@ -4855,7 +4855,7 @@
         <v>43</v>
       </c>
       <c r="N19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O19">
         <v>65</v>
@@ -4896,13 +4896,13 @@
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
         <v>31</v>
@@ -4914,13 +4914,13 @@
         <v>39</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s">
         <v>41</v>
       </c>
       <c r="I20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -4932,19 +4932,19 @@
         <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N20" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R20" t="s">
         <v>47</v>
@@ -4976,13 +4976,13 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
         <v>31</v>
@@ -4994,7 +4994,7 @@
         <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s">
         <v>41</v>
@@ -5012,19 +5012,19 @@
         <v>23</v>
       </c>
       <c r="M21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O21">
         <v>100</v>
       </c>
       <c r="P21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R21" t="s">
         <v>47</v>
@@ -5056,13 +5056,13 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D22" t="s">
         <v>31</v>
@@ -5071,7 +5071,7 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s">
         <v>40</v>
@@ -5080,7 +5080,7 @@
         <v>41</v>
       </c>
       <c r="I22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -5095,16 +5095,16 @@
         <v>43</v>
       </c>
       <c r="N22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O22">
         <v>65</v>
       </c>
       <c r="P22" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q22" t="s">
         <v>88</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>89</v>
       </c>
       <c r="R22" t="s">
         <v>47</v>
@@ -5136,13 +5136,13 @@
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
         <v>31</v>
@@ -5151,10 +5151,10 @@
         <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H23" t="s">
         <v>41</v>
@@ -5172,19 +5172,19 @@
         <v>23</v>
       </c>
       <c r="M23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N23" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R23" t="s">
         <v>47</v>
@@ -5216,13 +5216,13 @@
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
         <v>31</v>
@@ -5231,16 +5231,16 @@
         <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H24" t="s">
         <v>41</v>
       </c>
       <c r="I24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -5255,16 +5255,16 @@
         <v>43</v>
       </c>
       <c r="N24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O24">
         <v>65</v>
       </c>
       <c r="P24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="R24" t="s">
         <v>47</v>
@@ -5296,13 +5296,13 @@
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
         <v>31</v>
@@ -5311,16 +5311,16 @@
         <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H25" t="s">
         <v>41</v>
       </c>
       <c r="I25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J25">
         <v>4</v>
@@ -5332,19 +5332,19 @@
         <v>23</v>
       </c>
       <c r="M25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R25" t="s">
         <v>47</v>
@@ -5376,13 +5376,13 @@
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
         <v>50</v>
@@ -5415,7 +5415,7 @@
         <v>52</v>
       </c>
       <c r="N26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O26">
         <v>150</v>
@@ -5456,13 +5456,13 @@
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B27" t="s">
         <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
         <v>50</v>
@@ -5471,7 +5471,7 @@
         <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G27" t="s">
         <v>40</v>
@@ -5480,7 +5480,7 @@
         <v>41</v>
       </c>
       <c r="I27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -5495,16 +5495,16 @@
         <v>52</v>
       </c>
       <c r="N27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O27">
         <v>150</v>
       </c>
       <c r="P27" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q27" t="s">
         <v>88</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>89</v>
       </c>
       <c r="R27" t="s">
         <v>47</v>
@@ -5516,10 +5516,10 @@
         <v>23</v>
       </c>
       <c r="U27" t="s">
+        <v>91</v>
+      </c>
+      <c r="V27" t="s">
         <v>92</v>
-      </c>
-      <c r="V27" t="s">
-        <v>93</v>
       </c>
       <c r="W27" t="s">
         <v>23</v>
@@ -5552,7 +5552,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -5563,13 +5563,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -5591,19 +5591,19 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>16</v>
@@ -5611,7 +5611,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -5620,7 +5620,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -5631,7 +5631,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
@@ -5651,7 +5651,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
         <v>37</v>
@@ -5660,7 +5660,7 @@
         <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -5703,70 +5703,70 @@
   <sheetData>
     <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="W1" s="1" t="s">
         <v>16</v>
@@ -5774,82 +5774,82 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" t="s">
         <v>199</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>200</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
         <v>201</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" t="s">
         <v>202</v>
       </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>23</v>
-      </c>
-      <c r="R2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" t="s">
-        <v>23</v>
-      </c>
-      <c r="T2" t="s">
-        <v>23</v>
-      </c>
-      <c r="U2" t="s">
-        <v>23</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>203</v>
-      </c>
-      <c r="W2" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" t="s">
         <v>199</v>
       </c>
-      <c r="B3" t="s">
-        <v>200</v>
-      </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
@@ -5872,16 +5872,16 @@
         <v>23</v>
       </c>
       <c r="J3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K3" t="s">
         <v>205</v>
       </c>
-      <c r="K3" t="s">
-        <v>206</v>
-      </c>
       <c r="L3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N3" t="s">
         <v>52</v>
@@ -5908,7 +5908,7 @@
         <v>23</v>
       </c>
       <c r="V3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="W3" t="s">
         <v>23</v>
@@ -5916,11 +5916,11 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" t="s">
         <v>199</v>
       </c>
-      <c r="B4" t="s">
-        <v>200</v>
-      </c>
       <c r="C4" t="s">
         <v>23</v>
       </c>
@@ -5943,16 +5943,16 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
+        <v>204</v>
+      </c>
+      <c r="K4" t="s">
         <v>205</v>
       </c>
-      <c r="K4" t="s">
-        <v>206</v>
-      </c>
       <c r="L4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N4" t="s">
         <v>52</v>
@@ -5979,7 +5979,7 @@
         <v>23</v>
       </c>
       <c r="V4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="W4" t="s">
         <v>23</v>
@@ -6004,27 +6004,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
@@ -6064,10 +6064,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" t="s">
         <v>213</v>
-      </c>
-      <c r="B4" t="s">
-        <v>214</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -6084,10 +6084,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -6104,10 +6104,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -6130,7 +6130,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -6147,7 +6147,7 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>216</v>
       </c>
       <c r="C8" t="s">
         <v>217</v>
@@ -6353,7 +6353,7 @@
         <v>232</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>216</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -6406,12 +6406,12 @@
         <v>239</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -6438,7 +6438,7 @@
         <v>243</v>
       </c>
       <c r="B8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">

--- a/apps/web/public/examples/example-schedule.xlsx
+++ b/apps/web/public/examples/example-schedule.xlsx
@@ -733,7 +733,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>12:17:42</t>
+    <t>14:23:18</t>
   </si>
   <si>
     <t>Academic Year</t>

--- a/apps/web/public/examples/example-schedule.xlsx
+++ b/apps/web/public/examples/example-schedule.xlsx
@@ -733,7 +733,7 @@
     <t>Export Time</t>
   </si>
   <si>
-    <t>14:23:18</t>
+    <t>15:09:00</t>
   </si>
   <si>
     <t>Academic Year</t>
